--- a/RSL/formulario_extraccion_calidad.xlsx
+++ b/RSL/formulario_extraccion_calidad.xlsx
@@ -501,9 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -511,9 +508,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -549,9 +543,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -566,18 +557,12 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>Hoja 'Criterios': definición de cada pregunta de calidad y de cada campo.</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -913,31 +898,119 @@
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="4" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="n"/>
-      <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n"/>
-      <c r="AF3" s="4" t="n"/>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>300 reseñas de la App Store etiquetadas por los autores (de 932 388 reseñas de 40 apps)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>2 (150 y 150)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (muestra balanceada por diseño)</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>Autoetiquetado semisupervisado (self-training y otros) con k-NN, C4.5, NB y SVM</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 10 pliegues (DOB-SCV)</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud transductiva e inductiva</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Clasificación supervisada clásica</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>PR4</t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>Muestra pequeña balanceada artificialmente; útil como antecedente del aprendizaje semisupervisado, no del desbalance.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1101,31 +1174,123 @@
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="4" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="4" t="n"/>
-      <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="4" t="n"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (sin el único ejemplo de portabilidad)</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (elimina la clase con un solo ejemplo)</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>12 clasificadores de scikit-learn (NB, SVM, RL, DT, ET, KNN, MLP, propagación de etiquetas)</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada K-fold repetida</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 promediados por clase; varianza; tiempo de ejecución</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>RL 0.76 y SVM entre los mejores (F1 calculado con P y R promediados por clase)</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta por clase</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Comparación entre clasificadores</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF6" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH6" s="4" t="inlineStr">
+        <is>
+          <t>Los autores eliminan la clase PO por tener un solo ejemplo. Proponen como trabajo futuro aumentar los ejemplos con oraciones de Internet.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1165,31 +1330,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="n"/>
-      <c r="AE7" s="4" t="n"/>
-      <c r="AF7" s="4" t="n"/>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>NFRId: similitud semántica con Word2Vec y palabras clave (sin entrenamiento supervisado)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>Aplicación directa sobre todo el conjunto con umbral λ = 0.5</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase (TP, FP, FN)</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>Precisión media 0.53 y exhaustividad 0.83</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>PO 0.00; FT 0.12; MN 0.18; US 0.67</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Cleland-Huang et al. y Slankas y Williams</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>Precisión baja</t>
+        </is>
+      </c>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>Las clases raras (PO, FT, MN) quedan con F1 cercano a cero, incluso sin entrenamiento supervisado.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1293,31 +1550,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="n"/>
-      <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="n"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625); versión reetiquetada de Dalpiaz et al.; FR etiquetados por los autores</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR; 4 NFR frecuentes; 11 subclases de NFR; subclases de FR</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Submuestreo y sobremuestreo aleatorio en las tareas binarias muy desbalanceadas</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>BERT base y large (NoRBERT); comparado con SVM, NB y enfoques previos</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada 75/25; validación cruzada estratificada de 10 pliegues; validación por proyecto (p-fold)</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase; F1 promedio y ponderado</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR hasta 0.94 (proyectos vistos) y 0.92; clases NFR frecuentes 0.87 en promedio</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas; las clases raras quedan por debajo de las frecuentes</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Kurtanović y Maalej; Dalpiaz et al.; Abad et al.; Hussain et al.</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>Prueba t pareada (p = 0.0136). Reconoce que PROMISE contiene duplicados y etiquetas erróneas. El sobremuestreo replica la clase minoritaria solo dentro del entrenamiento. Código y datos en Zenodo (10.5281/zenodo.3833660).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1965,31 +2314,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="n"/>
-      <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
-      <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n"/>
-      <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="4" t="n"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625) y versión reetiquetada (612); Concordia RE corpus</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>625 / 612</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR; 4 subclases NFR frecuentes; generalización entre conjuntos</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna; restringe la tarea multiclase a las 4 subclases con más de 50 ejemplos</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>DBGAT (BERT + red de atención sobre grafos de dependencias); ML, DL, NoRBERT</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 10 pliegues y por proyecto (p-fold)</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y20" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, F1 y F1 promedio ponderado</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="inlineStr">
+        <is>
+          <t>Hasta 0.91 (proyectos vistos) y 0.88 (no vistos); 0.83 en conjuntos heterogéneos</t>
+        </is>
+      </c>
+      <c r="AB20" s="4" t="inlineStr">
+        <is>
+          <t>No aplica (excluye las clases raras)</t>
+        </is>
+      </c>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>NB, RF, Kurtanović y Maalej, NoRBERT, Abad et al.</t>
+        </is>
+      </c>
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF20" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG20" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR5</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
+          <t>Usa la versión reetiquetada que corrige duplicados y etiquetas erróneas. Evita el desbalance seleccionando solo las 4 subclases frecuentes, lo que deja fuera las clases raras.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2665,31 +3106,127 @@
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="4" t="n"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
-      <c r="R31" s="4" t="n"/>
-      <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
-      <c r="U31" s="4" t="n"/>
-      <c r="V31" s="4" t="n"/>
-      <c r="W31" s="4" t="n"/>
-      <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="4" t="n"/>
-      <c r="Z31" s="4" t="n"/>
-      <c r="AA31" s="4" t="n"/>
-      <c r="AB31" s="4" t="n"/>
-      <c r="AC31" s="4" t="n"/>
-      <c r="AD31" s="4" t="n"/>
-      <c r="AE31" s="4" t="n"/>
-      <c r="AF31" s="4" t="n"/>
-      <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="4" t="n"/>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE_exp</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>Descomposición del entrenamiento en dos subconjuntos balanceados y clasificación jerárquica (HC4RC)</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>HC4RC (SVM con selección de rasgos por roles semánticos); K&amp;M, Yin y NoRBERT reimplementados</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada de 10 pliegues y por proyecto (p-fold)</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y31" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase; promedios macro y micro</t>
+        </is>
+      </c>
+      <c r="Z31" s="4" t="inlineStr">
+        <is>
+          <t>HC4RC 0.51 (10-fold) y 0.50 (p-fold); K&amp;M 0.44 / 0.39; Yin 0.47 / 0.22; NoRBERT el más alto</t>
+        </is>
+      </c>
+      <c r="AA31" s="4" t="inlineStr">
+        <is>
+          <t>Micro: HC4RC 0.63 / 0.64; K&amp;M 0.58 / 0.61</t>
+        </is>
+      </c>
+      <c r="AB31" s="4" t="inlineStr">
+        <is>
+          <t>Por clase; HC4RC gana en A, MN y L; NoRBERT en FT y PO</t>
+        </is>
+      </c>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>Kurtanović y Maalej, Yin et al., NoRBERT</t>
+        </is>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE31" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF31" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG31" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
+          <t>Critica que NoRBERT reporte F1 ponderado, que favorece a las clases mayoritarias, y defiende el F1 macro. Argumenta que el sobremuestreo puede sobreajustar a las clases minoritarias. Código en Zenodo.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -3277,31 +3814,123 @@
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="4" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
-      <c r="O41" s="4" t="n"/>
-      <c r="P41" s="4" t="n"/>
-      <c r="Q41" s="4" t="n"/>
-      <c r="R41" s="4" t="n"/>
-      <c r="S41" s="4" t="n"/>
-      <c r="T41" s="4" t="n"/>
-      <c r="U41" s="4" t="n"/>
-      <c r="V41" s="4" t="n"/>
-      <c r="W41" s="4" t="n"/>
-      <c r="X41" s="4" t="n"/>
-      <c r="Y41" s="4" t="n"/>
-      <c r="Z41" s="4" t="n"/>
-      <c r="AA41" s="4" t="n"/>
-      <c r="AB41" s="4" t="n"/>
-      <c r="AC41" s="4" t="n"/>
-      <c r="AD41" s="4" t="n"/>
-      <c r="AE41" s="4" t="n"/>
-      <c r="AF41" s="4" t="n"/>
-      <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="4" t="n"/>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625); SecReq (510)</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>625 y 510</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR; clases NFR; seguridad/no seguridad</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (zero-shot)</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>Zero-shot con SBERT, AllMiniLM, BERT4RE y SObert</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>Sin entrenamiento; evaluación sobre el conjunto completo</t>
+        </is>
+      </c>
+      <c r="X41" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="Y41" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 ponderados y por clase</t>
+        </is>
+      </c>
+      <c r="Z41" s="4" t="inlineStr"/>
+      <c r="AA41" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR 0.66; NFR frecuentes 0.72–0.80; seguridad 0.66</t>
+        </is>
+      </c>
+      <c r="AB41" s="4" t="inlineStr">
+        <is>
+          <t>Más bajo en las clases raras (anexo en GitHub)</t>
+        </is>
+      </c>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Enfoques supervisados (NoRBERT y otros)</t>
+        </is>
+      </c>
+      <c r="AD41" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE41" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF41" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG41" s="4" t="inlineStr">
+        <is>
+          <t>PR3</t>
+        </is>
+      </c>
+      <c r="AH41" s="4" t="inlineStr">
+        <is>
+          <t>ANOVA de medidas repetidas y prueba de Friedman. Código en github.com/waadalhoshan/ZSL4REQ.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -3777,31 +4406,123 @@
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="4" t="n"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="n"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
-      <c r="O49" s="4" t="n"/>
-      <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
-      <c r="R49" s="4" t="n"/>
-      <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n"/>
-      <c r="U49" s="4" t="n"/>
-      <c r="V49" s="4" t="n"/>
-      <c r="W49" s="4" t="n"/>
-      <c r="X49" s="4" t="n"/>
-      <c r="Y49" s="4" t="n"/>
-      <c r="Z49" s="4" t="n"/>
-      <c r="AA49" s="4" t="n"/>
-      <c r="AB49" s="4" t="n"/>
-      <c r="AC49" s="4" t="n"/>
-      <c r="AD49" s="4" t="n"/>
-      <c r="AE49" s="4" t="n"/>
-      <c r="AF49" s="4" t="n"/>
-      <c r="AG49" s="4" t="n"/>
-      <c r="AH49" s="4" t="n"/>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE_exp</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>Subclases de NFR de PROMISE_exp</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>Sobremuestreo (imbalanced-learn)</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>SVM, RL, KNN, NB, votación; Bi-LSTM; híbrido Bi-LSTM + SVM</t>
+        </is>
+      </c>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 10 pliegues sobre el conjunto ya sobremuestreado</t>
+        </is>
+      </c>
+      <c r="X49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y49" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1 por pliegue</t>
+        </is>
+      </c>
+      <c r="Z49" s="4" t="inlineStr"/>
+      <c r="AA49" s="4" t="inlineStr">
+        <is>
+          <t>Híbrido ≈ 0.98–0.99 en todos los pliegues</t>
+        </is>
+      </c>
+      <c r="AB49" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta por clase</t>
+        </is>
+      </c>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Modelos propios de ML y DL</t>
+        </is>
+      </c>
+      <c r="AD49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF49" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG49" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH49" s="4" t="inlineStr">
+        <is>
+          <t>El sobremuestreo se aplica a todo el conjunto (Fig. 2, 'oversampled dataset') antes de la validación cruzada, así que las copias de un mismo requerimiento pueden quedar en entrenamiento y prueba. Las exactitudes &gt; 0.98 son consistentes con esa fuga.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -3837,31 +4558,123 @@
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="4" t="n"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="n"/>
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
-      <c r="O50" s="4" t="n"/>
-      <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n"/>
-      <c r="R50" s="4" t="n"/>
-      <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n"/>
-      <c r="U50" s="4" t="n"/>
-      <c r="V50" s="4" t="n"/>
-      <c r="W50" s="4" t="n"/>
-      <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="4" t="n"/>
-      <c r="Z50" s="4" t="n"/>
-      <c r="AA50" s="4" t="n"/>
-      <c r="AB50" s="4" t="n"/>
-      <c r="AC50" s="4" t="n"/>
-      <c r="AD50" s="4" t="n"/>
-      <c r="AE50" s="4" t="n"/>
-      <c r="AF50" s="4" t="n"/>
-      <c r="AG50" s="4" t="n"/>
-      <c r="AH50" s="4" t="n"/>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (12 clases); además defectos y conflictos (otras tareas)</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>Sobremuestreo y submuestreo</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>NLI con RoBERTa; ChatGPT, modelo de prompts, BERT y clasificadores estadísticos</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>Partición 80/10/10 y validación cruzada de 10 pliegues; escenarios supervisado y zero-shot</t>
+        </is>
+      </c>
+      <c r="X50" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y50" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase</t>
+        </is>
+      </c>
+      <c r="Z50" s="4" t="inlineStr"/>
+      <c r="AA50" s="4" t="inlineStr">
+        <is>
+          <t>NLI &gt; 0.83 en clasificación de requerimientos</t>
+        </is>
+      </c>
+      <c r="AB50" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas (PO con 1 ejemplo)</t>
+        </is>
+      </c>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>ChatGPT, prompt learning, BERT y modelos probabilísticos</t>
+        </is>
+      </c>
+      <c r="AD50" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE50" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF50" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas y limitaciones</t>
+        </is>
+      </c>
+      <c r="AG50" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR3</t>
+        </is>
+      </c>
+      <c r="AH50" s="4" t="inlineStr">
+        <is>
+          <t>El conjunto de prueba se mantiene sin alterar al remuestrear (buena práctica).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -3901,31 +4714,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-      <c r="O51" s="4" t="n"/>
-      <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n"/>
-      <c r="R51" s="4" t="n"/>
-      <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
-      <c r="U51" s="4" t="n"/>
-      <c r="V51" s="4" t="n"/>
-      <c r="W51" s="4" t="n"/>
-      <c r="X51" s="4" t="n"/>
-      <c r="Y51" s="4" t="n"/>
-      <c r="Z51" s="4" t="n"/>
-      <c r="AA51" s="4" t="n"/>
-      <c r="AB51" s="4" t="n"/>
-      <c r="AC51" s="4" t="n"/>
-      <c r="AD51" s="4" t="n"/>
-      <c r="AE51" s="4" t="n"/>
-      <c r="AF51" s="4" t="n"/>
-      <c r="AG51" s="4" t="n"/>
-      <c r="AH51" s="4" t="n"/>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE multietiqueta; EHR-binario; EHR-multiclase (5722 requerimientos); caso de estudio con reseñas de software</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE multietiqueta (792 instancias según la Fig. 4); EHR 5722</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Multietiqueta</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE: 19 etiquetas</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna específica; transforma multietiqueta en multiclase (label powerset)</t>
+        </is>
+      </c>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U51" s="4" t="inlineStr">
+        <is>
+          <t>OkapiBM25 + regresión logística (propuesto); 123 pipelines de ML y 9 de DL con word2vec y FastText; BERT en el caso de estudio</t>
+        </is>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada de 10 pliegues; hiperparámetros con PSO</t>
+        </is>
+      </c>
+      <c r="X51" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y51" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1, en versiones micro y macro (8 medidas)</t>
+        </is>
+      </c>
+      <c r="Z51" s="4" t="inlineStr">
+        <is>
+          <t>Mejora de 13 % en F1 macro sobre el mejor predictor previo en PROMISE (valor absoluto en tablas de resultados)</t>
+        </is>
+      </c>
+      <c r="AA51" s="4" t="inlineStr"/>
+      <c r="AB51" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta en el texto revisado</t>
+        </is>
+      </c>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Predictor del estado del arte en multietiqueta; 132 pipelines de ML y DL; BERT en reseñas</t>
+        </is>
+      </c>
+      <c r="AD51" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE51" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF51" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones en el texto revisado</t>
+        </is>
+      </c>
+      <c r="AG51" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH51" s="4" t="inlineStr">
+        <is>
+          <t>El texto del PDF pierde las cifras por la fuente; los valores se leyeron de las páginas 1 y 12 como imagen. Supera a BERT en 1.4 puntos de F1 en reseñas.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -3961,8 +4866,16 @@
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>CE2</t>
+        </is>
+      </c>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
@@ -3985,7 +4898,11 @@
       <c r="AE52" s="4" t="n"/>
       <c r="AF52" s="4" t="n"/>
       <c r="AG52" s="4" t="n"/>
-      <c r="AH52" s="4" t="n"/>
+      <c r="AH52" s="4" t="inlineStr">
+        <is>
+          <t>Asigna requerimientos regulatorios a etiquetas de taxonomías de dominio (250–1183 clases) para trazabilidad; las clases no son tipos de requerimiento ni atributos de calidad.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -4505,31 +5422,123 @@
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="4" t="n"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
-      <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
-      <c r="O61" s="4" t="n"/>
-      <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n"/>
-      <c r="R61" s="4" t="n"/>
-      <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
-      <c r="U61" s="4" t="n"/>
-      <c r="V61" s="4" t="n"/>
-      <c r="W61" s="4" t="n"/>
-      <c r="X61" s="4" t="n"/>
-      <c r="Y61" s="4" t="n"/>
-      <c r="Z61" s="4" t="n"/>
-      <c r="AA61" s="4" t="n"/>
-      <c r="AB61" s="4" t="n"/>
-      <c r="AC61" s="4" t="n"/>
-      <c r="AD61" s="4" t="n"/>
-      <c r="AE61" s="4" t="n"/>
-      <c r="AF61" s="4" t="n"/>
-      <c r="AG61" s="4" t="n"/>
-      <c r="AH61" s="4" t="n"/>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Software Requirements Dataset de Kaggle (977 filas; 976 tras quitar duplicados)</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>No se precisa en el texto revisado</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U61" s="4" t="inlineStr">
+        <is>
+          <t>Prototypical Networks, Matching Networks, MAML (aprendizaje few-shot)</t>
+        </is>
+      </c>
+      <c r="V61" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W61" s="4" t="inlineStr">
+        <is>
+          <t>Partición 80/20; los autores escriben que 'es probable' que se haya usado muestreo estratificado</t>
+        </is>
+      </c>
+      <c r="X61" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y61" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión y exhaustividad</t>
+        </is>
+      </c>
+      <c r="Z61" s="4" t="inlineStr"/>
+      <c r="AA61" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud: Prototypical 0.82; MAML 0.769</t>
+        </is>
+      </c>
+      <c r="AB61" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Comparación entre algoritmos few-shot</t>
+        </is>
+      </c>
+      <c r="AD61" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE61" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF61" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG61" s="4" t="inlineStr">
+        <is>
+          <t>PR4</t>
+        </is>
+      </c>
+      <c r="AH61" s="4" t="inlineStr">
+        <is>
+          <t>Quita duplicados antes de partir (buena práctica). El protocolo de partición no está descrito con certeza por los propios autores.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -4573,31 +5582,123 @@
           <t>PROMISE; SecReq</t>
         </is>
       </c>
-      <c r="J62" s="4" t="n"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
-      <c r="O62" s="4" t="n"/>
-      <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n"/>
-      <c r="R62" s="4" t="n"/>
-      <c r="S62" s="4" t="n"/>
-      <c r="T62" s="4" t="n"/>
-      <c r="U62" s="4" t="n"/>
-      <c r="V62" s="4" t="n"/>
-      <c r="W62" s="4" t="n"/>
-      <c r="X62" s="4" t="n"/>
-      <c r="Y62" s="4" t="n"/>
-      <c r="Z62" s="4" t="n"/>
-      <c r="AA62" s="4" t="n"/>
-      <c r="AB62" s="4" t="n"/>
-      <c r="AC62" s="4" t="n"/>
-      <c r="AD62" s="4" t="n"/>
-      <c r="AE62" s="4" t="n"/>
-      <c r="AF62" s="4" t="n"/>
-      <c r="AG62" s="4" t="n"/>
-      <c r="AH62" s="4" t="n"/>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR; SecReq</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625) y SecReq</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>FR-NFR: 2; MC-NFR: 10; Sec-NonSec: 2</t>
+        </is>
+      </c>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (prompting); usa F1 macro por el desbalance</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U62" s="4" t="inlineStr">
+        <is>
+          <t>Claude 3 Haiku, DeepSeek-V3, Gemini, GPT-4 Turbo, Llama 3.2 3B; BERT ajustado como referencia</t>
+        </is>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador few-shot</t>
+        </is>
+      </c>
+      <c r="W62" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada 8:1:1 (entrenamiento/validación/prueba); zero-shot, few-shot (1, 3, 5), persona y CoT</t>
+        </is>
+      </c>
+      <c r="X62" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y62" s="4" t="inlineStr">
+        <is>
+          <t>F1 macro (principal); resto en anexo en línea</t>
+        </is>
+      </c>
+      <c r="Z62" s="4" t="inlineStr">
+        <is>
+          <t>Mejor: FR-NFR 0.92 (Gemini 5FS), MC-NFR 0.94 (DeepSeek 3FS+persona); zero-shot MC-NFR hasta 0.88</t>
+        </is>
+      </c>
+      <c r="AA62" s="4" t="inlineStr"/>
+      <c r="AB62" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta en el artículo (anexo en línea)</t>
+        </is>
+      </c>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>BERT ajustado (estado del arte)</t>
+        </is>
+      </c>
+      <c r="AD62" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE62" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF62" s="4" t="inlineStr">
+        <is>
+          <t>Amenazas a la validez: dependencia de APIs, variabilidad de los LLM, solo dos conjuntos en inglés</t>
+        </is>
+      </c>
+      <c r="AG62" s="4" t="inlineStr">
+        <is>
+          <t>PR3, PR5</t>
+        </is>
+      </c>
+      <c r="AH62" s="4" t="inlineStr">
+        <is>
+          <t>Pruebas Scott-Knott ESD con tamaño del efecto de Cliff. Prompts y resultados completos en OSF. El transformer de referencia no usa datos aumentados.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -4821,8 +5922,16 @@
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>CE2</t>
+        </is>
+      </c>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
       <c r="N66" s="4" t="n"/>
@@ -4845,7 +5954,11 @@
       <c r="AE66" s="4" t="n"/>
       <c r="AF66" s="4" t="n"/>
       <c r="AG66" s="4" t="n"/>
-      <c r="AH66" s="4" t="n"/>
+      <c r="AH66" s="4" t="inlineStr">
+        <is>
+          <t>Réplica de Mekala et al. (RE 2021): clasifica reseñas de apps en útiles o inútiles para requerimientos (Helpful/Useless), no por tipo de requerimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -5333,31 +6446,127 @@
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="4" t="n"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n"/>
-      <c r="P74" s="4" t="n"/>
-      <c r="Q74" s="4" t="n"/>
-      <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="n"/>
-      <c r="T74" s="4" t="n"/>
-      <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n"/>
-      <c r="W74" s="4" t="n"/>
-      <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="n"/>
-      <c r="Z74" s="4" t="n"/>
-      <c r="AA74" s="4" t="n"/>
-      <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="4" t="n"/>
-      <c r="AD74" s="4" t="n"/>
-      <c r="AE74" s="4" t="n"/>
-      <c r="AF74" s="4" t="n"/>
-      <c r="AG74" s="4" t="n"/>
-      <c r="AH74" s="4" t="n"/>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto publicado por los autores (derivado de PROMISE; 1,534 filas, 988 requerimientos distintos tras deduplicar)</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>1534 (1073 entrenamiento / 461 prueba)</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S74" s="4" t="inlineStr">
+        <is>
+          <t>TAOS: 7 aumentadores de TextAttack (WordNet, Embedding, CharSwap, Deletion, EDA, CheckList, CLARE) con filtro de paráfrasis τ = 0.70</t>
+        </is>
+      </c>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U74" s="4" t="inlineStr">
+        <is>
+          <t>BERT base uncased</t>
+        </is>
+      </c>
+      <c r="V74" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W74" s="4" t="inlineStr">
+        <is>
+          <t>Partición fija 70/30 (1073/461); 3 épocas</t>
+        </is>
+      </c>
+      <c r="X74" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y74" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, F1 ponderado, F1 macro, F1 por clase, matriz de confusión</t>
+        </is>
+      </c>
+      <c r="Z74" s="4" t="inlineStr">
+        <is>
+          <t>0.89 (línea base 0.44)</t>
+        </is>
+      </c>
+      <c r="AA74" s="4" t="inlineStr">
+        <is>
+          <t>0.93 (línea base 0.75)</t>
+        </is>
+      </c>
+      <c r="AB74" s="4" t="inlineStr">
+        <is>
+          <t>MN 0.90, L 1.00, FT 0.86, PO 0.50 (línea base: 0.00 en las cuatro)</t>
+        </is>
+      </c>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>BERT sin aumentación</t>
+        </is>
+      </c>
+      <c r="AD74" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE74" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF74" s="4" t="inlineStr">
+        <is>
+          <t>Ruido de los datos sintéticos; un solo conjunto; taxonomía única; tiempo de entrenamiento 4 veces mayor</t>
+        </is>
+      </c>
+      <c r="AG74" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH74" s="4" t="inlineStr">
+        <is>
+          <t>Verificación propia del repositorio: 240 de 461 requerimientos de prueba (52 %) repetidos en entrenamiento. La Fig. 1 muestra una clase 'NFR' (110) ajena a las 12 clases.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -5461,31 +6670,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J76" s="4" t="n"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="n"/>
-      <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n"/>
-      <c r="O76" s="4" t="n"/>
-      <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n"/>
-      <c r="R76" s="4" t="n"/>
-      <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="n"/>
-      <c r="U76" s="4" t="n"/>
-      <c r="V76" s="4" t="n"/>
-      <c r="W76" s="4" t="n"/>
-      <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="4" t="n"/>
-      <c r="Z76" s="4" t="n"/>
-      <c r="AA76" s="4" t="n"/>
-      <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="4" t="n"/>
-      <c r="AD76" s="4" t="n"/>
-      <c r="AE76" s="4" t="n"/>
-      <c r="AF76" s="4" t="n"/>
-      <c r="AG76" s="4" t="n"/>
-      <c r="AH76" s="4" t="n"/>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>Muestra estratificada de 1000 reseñas (de 132 194 de tres tiendas); gold standards propios</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>Relevancia (útil/inútil) y características de calidad basadas en ISO/IEC 25010</t>
+        </is>
+      </c>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S76" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U76" s="4" t="inlineStr">
+        <is>
+          <t>Patrones lingüísticos por palabras clave; crowdsourcing (Kyōryoku); ChatGPT 4 y 4o zero-shot y few-shot</t>
+        </is>
+      </c>
+      <c r="V76" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W76" s="4" t="inlineStr">
+        <is>
+          <t>Comparación de los tres enfoques contra el gold standard; sin entrenamiento supervisado</t>
+        </is>
+      </c>
+      <c r="X76" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="Y76" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión y exhaustividad por clase</t>
+        </is>
+      </c>
+      <c r="Z76" s="4" t="inlineStr"/>
+      <c r="AA76" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase de calidad: crowdsourcing 0.63–0.72, mejor condición de ChatGPT 0.66, voto mayoritario 0.68 (exactitud)</t>
+        </is>
+      </c>
+      <c r="AB76" s="4" t="inlineStr">
+        <is>
+          <t>Precisión de los patrones entre 0.38 y 0.92 según la característica</t>
+        </is>
+      </c>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Patrones lingüísticos como línea base</t>
+        </is>
+      </c>
+      <c r="AD76" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE76" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF76" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG76" s="4" t="inlineStr">
+        <is>
+          <t>PR3, PR4</t>
+        </is>
+      </c>
+      <c r="AH76" s="4" t="inlineStr">
+        <is>
+          <t>Preprint en arXiv (sometido a Elsevier). Friedman y Wilcoxon con Bonferroni. Los LLM sobreclasifican la clase 'útil': sesgo hacia la clase mayoritaria. Un LLM iguala a un grupo de evaluadores legos, no lo supera.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -5961,31 +7262,123 @@
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="4" t="n"/>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n"/>
-      <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
-      <c r="O84" s="4" t="n"/>
-      <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n"/>
-      <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="n"/>
-      <c r="U84" s="4" t="n"/>
-      <c r="V84" s="4" t="n"/>
-      <c r="W84" s="4" t="n"/>
-      <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
-      <c r="Z84" s="4" t="n"/>
-      <c r="AA84" s="4" t="n"/>
-      <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="n"/>
-      <c r="AE84" s="4" t="n"/>
-      <c r="AF84" s="4" t="n"/>
-      <c r="AG84" s="4" t="n"/>
-      <c r="AH84" s="4" t="n"/>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>1880 reseñas anotadas de 10 apps (Google Play y App Store)</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>1880</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>4 (FR 712, NFR 654, ambos 298, ninguno 216)</t>
+        </is>
+      </c>
+      <c r="R84" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S84" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U84" s="4" t="inlineStr">
+        <is>
+          <t>GPT-4o mini (zero-shot); RF, DT, SVC, XGBoost, RL</t>
+        </is>
+      </c>
+      <c r="V84" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W84" s="4" t="inlineStr">
+        <is>
+          <t>Zero-shot con 3 prompts y 3 temperaturas; ML clásico en partición de prueba</t>
+        </is>
+      </c>
+      <c r="X84" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y84" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 micro</t>
+        </is>
+      </c>
+      <c r="Z84" s="4" t="inlineStr"/>
+      <c r="AA84" s="4" t="inlineStr">
+        <is>
+          <t>F1 micro 0.842 (temperatura 0.2); ML clásico ≤ 0.49</t>
+        </is>
+      </c>
+      <c r="AB84" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Cinco modelos de ML clásico</t>
+        </is>
+      </c>
+      <c r="AD84" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE84" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF84" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG84" s="4" t="inlineStr">
+        <is>
+          <t>PR3, PR4</t>
+        </is>
+      </c>
+      <c r="AH84" s="4" t="inlineStr">
+        <is>
+          <t>La temperatura afecta el resultado (mejor a 0.2). Anotación por 5 ingenieros con consenso mayoritario.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -6089,31 +7482,123 @@
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="4" t="n"/>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K86" s="4" t="n"/>
-      <c r="L86" s="4" t="n"/>
-      <c r="M86" s="4" t="n"/>
-      <c r="N86" s="4" t="n"/>
-      <c r="O86" s="4" t="n"/>
-      <c r="P86" s="4" t="n"/>
-      <c r="Q86" s="4" t="n"/>
-      <c r="R86" s="4" t="n"/>
-      <c r="S86" s="4" t="n"/>
-      <c r="T86" s="4" t="n"/>
-      <c r="U86" s="4" t="n"/>
-      <c r="V86" s="4" t="n"/>
-      <c r="W86" s="4" t="n"/>
-      <c r="X86" s="4" t="n"/>
-      <c r="Y86" s="4" t="n"/>
-      <c r="Z86" s="4" t="n"/>
-      <c r="AA86" s="4" t="n"/>
-      <c r="AB86" s="4" t="n"/>
-      <c r="AC86" s="4" t="n"/>
-      <c r="AD86" s="4" t="n"/>
-      <c r="AE86" s="4" t="n"/>
-      <c r="AF86" s="4" t="n"/>
-      <c r="AG86" s="4" t="n"/>
-      <c r="AH86" s="4" t="n"/>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR; conjunto sintético generado con GPT-4o (10 veces PROMISE); PURE NFR (compilado por los autores)</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE 625; sintético ≈10× PROMISE</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>11 (experimento 1); 5 (experimento 2, PURE)</t>
+        </is>
+      </c>
+      <c r="R86" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S86" s="4" t="inlineStr">
+        <is>
+          <t>Generación de NFR sintéticos con GPT-4o (plantillas de prompt por clase)</t>
+        </is>
+      </c>
+      <c r="T86" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U86" s="4" t="inlineStr">
+        <is>
+          <t>SVM, Naive Bayes, BERT base uncased</t>
+        </is>
+      </c>
+      <c r="V86" s="4" t="inlineStr">
+        <is>
+          <t>Generador de datos</t>
+        </is>
+      </c>
+      <c r="W86" s="4" t="inlineStr">
+        <is>
+          <t>Exp. 1: partición 70/30 de PROMISE; Exp. 2: entrenar con sintético y probar en PURE NFR (TSTR)</t>
+        </is>
+      </c>
+      <c r="X86" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase y ponderados</t>
+        </is>
+      </c>
+      <c r="Z86" s="4" t="inlineStr"/>
+      <c r="AA86" s="4" t="inlineStr">
+        <is>
+          <t>Exp. 1 (PROMISE): BERT-real 0.80, BERT-combinado 0.77, BERT-sintético 0.51. Exp. 2 (PURE): combinado ≈0.63</t>
+        </is>
+      </c>
+      <c r="AB86" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en Tablas III–IV</t>
+        </is>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Modelos entrenados solo con PROMISE</t>
+        </is>
+      </c>
+      <c r="AD86" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE86" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF86" s="4" t="inlineStr">
+        <is>
+          <t>Reducción a 5 clases en PURE; tamaño y desbalance de PROMISE; posible sesgo del LLM</t>
+        </is>
+      </c>
+      <c r="AG86" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH86" s="4" t="inlineStr">
+        <is>
+          <t>Matiz frente al resumen: en PROMISE, el modelo entrenado solo con datos reales supera al combinado y al sintético; la ventaja del sintético aparece solo al probar en PURE. Revisa duplicados exactos en el conjunto sintético.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -6153,31 +7638,123 @@
           <t>PROMISE; PURE</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n"/>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="n"/>
-      <c r="L87" s="4" t="n"/>
-      <c r="M87" s="4" t="n"/>
-      <c r="N87" s="4" t="n"/>
-      <c r="O87" s="4" t="n"/>
-      <c r="P87" s="4" t="n"/>
-      <c r="Q87" s="4" t="n"/>
-      <c r="R87" s="4" t="n"/>
-      <c r="S87" s="4" t="n"/>
-      <c r="T87" s="4" t="n"/>
-      <c r="U87" s="4" t="n"/>
-      <c r="V87" s="4" t="n"/>
-      <c r="W87" s="4" t="n"/>
-      <c r="X87" s="4" t="n"/>
-      <c r="Y87" s="4" t="n"/>
-      <c r="Z87" s="4" t="n"/>
-      <c r="AA87" s="4" t="n"/>
-      <c r="AB87" s="4" t="n"/>
-      <c r="AC87" s="4" t="n"/>
-      <c r="AD87" s="4" t="n"/>
-      <c r="AE87" s="4" t="n"/>
-      <c r="AF87" s="4" t="n"/>
-      <c r="AG87" s="4" t="n"/>
-      <c r="AH87" s="4" t="n"/>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (625: 254 FR, 371 NFR); además PURE, REQuestA y Aerospace (otras tareas)</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>No se precisa en el texto revisado (comparan contra el estado del arte en PROMISE)</t>
+        </is>
+      </c>
+      <c r="R87" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="S87" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T87" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U87" s="4" t="inlineStr">
+        <is>
+          <t>ChatGPT y Gemini con prompts de tres niveles de conocimiento experto</t>
+        </is>
+      </c>
+      <c r="V87" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W87" s="4" t="inlineStr">
+        <is>
+          <t>Solo los conjuntos de prueba de las particiones estándar; cinco particiones aleatorias promediadas</t>
+        </is>
+      </c>
+      <c r="X87" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y87" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, F1 y promedio ponderado</t>
+        </is>
+      </c>
+      <c r="Z87" s="4" t="inlineStr"/>
+      <c r="AA87" s="4" t="inlineStr">
+        <is>
+          <t>ChatGPT y Gemini 0.78 frente a 0.96 del mejor predictor específico</t>
+        </is>
+      </c>
+      <c r="AB87" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Predictores de ML/DL específicos de la tarea y modelos de lenguaje tradicionales</t>
+        </is>
+      </c>
+      <c r="AD87" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE87" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF87" s="4" t="inlineStr">
+        <is>
+          <t>Inestabilidad de las predicciones entre iteraciones del mismo prompt</t>
+        </is>
+      </c>
+      <c r="AG87" s="4" t="inlineStr">
+        <is>
+          <t>PR3</t>
+        </is>
+      </c>
+      <c r="AH87" s="4" t="inlineStr">
+        <is>
+          <t>Los LLM generativos quedan 18 puntos por debajo de los modelos ajustados en clasificación. Señalan que los LLM tienen dificultades con el equilibrio entre precisión y exhaustividad.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -6337,31 +7914,123 @@
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="4" t="n"/>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K90" s="4" t="n"/>
-      <c r="L90" s="4" t="n"/>
-      <c r="M90" s="4" t="n"/>
-      <c r="N90" s="4" t="n"/>
-      <c r="O90" s="4" t="n"/>
-      <c r="P90" s="4" t="n"/>
-      <c r="Q90" s="4" t="n"/>
-      <c r="R90" s="4" t="n"/>
-      <c r="S90" s="4" t="n"/>
-      <c r="T90" s="4" t="n"/>
-      <c r="U90" s="4" t="n"/>
-      <c r="V90" s="4" t="n"/>
-      <c r="W90" s="4" t="n"/>
-      <c r="X90" s="4" t="n"/>
-      <c r="Y90" s="4" t="n"/>
-      <c r="Z90" s="4" t="n"/>
-      <c r="AA90" s="4" t="n"/>
-      <c r="AB90" s="4" t="n"/>
-      <c r="AC90" s="4" t="n"/>
-      <c r="AD90" s="4" t="n"/>
-      <c r="AE90" s="4" t="n"/>
-      <c r="AF90" s="4" t="n"/>
-      <c r="AG90" s="4" t="n"/>
-      <c r="AH90" s="4" t="n"/>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>Instagram App Reviews (Kaggle, 209,956 reseñas), submuestra de 5000 reetiquetada por aspectos</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>5000 reseñas</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>3 métricas de usabilidad (completitud, corrección, satisfacción) con polaridad</t>
+        </is>
+      </c>
+      <c r="R90" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S90" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T90" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U90" s="4" t="inlineStr">
+        <is>
+          <t>BERT-BiLSTM-CNN (propuesto); BERT, BERT-RNN y otros modelos DL</t>
+        </is>
+      </c>
+      <c r="V90" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W90" s="4" t="inlineStr">
+        <is>
+          <t>Partición 70/30 y validación cruzada de 10 pliegues en el entrenamiento</t>
+        </is>
+      </c>
+      <c r="X90" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y90" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, F1 y exactitud</t>
+        </is>
+      </c>
+      <c r="Z90" s="4" t="inlineStr"/>
+      <c r="AA90" s="4" t="inlineStr">
+        <is>
+          <t>F1 0.91, exactitud 0.94 (no especifica el promedio)</t>
+        </is>
+      </c>
+      <c r="AB90" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>BERT y arquitecturas híbridas BERT-RNN</t>
+        </is>
+      </c>
+      <c r="AD90" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE90" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF90" s="4" t="inlineStr">
+        <is>
+          <t>Costo computacional, dependencia de datos etiquetados, escalabilidad a otros idiomas</t>
+        </is>
+      </c>
+      <c r="AG90" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH90" s="4" t="inlineStr">
+        <is>
+          <t>Distribución sesgada: satisfacción 2594, corrección 930, completitud 527. El conjunto original es público en Kaggle; el reetiquetado no se indica como público.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -6401,31 +8070,123 @@
           <t>PURE</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n"/>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
-      <c r="N91" s="4" t="n"/>
-      <c r="O91" s="4" t="n"/>
-      <c r="P91" s="4" t="n"/>
-      <c r="Q91" s="4" t="n"/>
-      <c r="R91" s="4" t="n"/>
-      <c r="S91" s="4" t="n"/>
-      <c r="T91" s="4" t="n"/>
-      <c r="U91" s="4" t="n"/>
-      <c r="V91" s="4" t="n"/>
-      <c r="W91" s="4" t="n"/>
-      <c r="X91" s="4" t="n"/>
-      <c r="Y91" s="4" t="n"/>
-      <c r="Z91" s="4" t="n"/>
-      <c r="AA91" s="4" t="n"/>
-      <c r="AB91" s="4" t="n"/>
-      <c r="AC91" s="4" t="n"/>
-      <c r="AD91" s="4" t="n"/>
-      <c r="AE91" s="4" t="n"/>
-      <c r="AF91" s="4" t="n"/>
-      <c r="AG91" s="4" t="n"/>
-      <c r="AH91" s="4" t="n"/>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>PURE (79 documentos de requerimientos no estructurados)</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>No se precisa en el texto revisado</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>5 (fiabilidad, desempeño, seguridad, disponibilidad, usabilidad) más FR</t>
+        </is>
+      </c>
+      <c r="R91" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S91" s="4" t="inlineStr">
+        <is>
+          <t>Remuestreo: SMOTE para la clase minoritaria y submuestreo de la mayoritaria</t>
+        </is>
+      </c>
+      <c r="T91" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="U91" s="4" t="inlineStr">
+        <is>
+          <t>NB, SVM, LR y CNN con BoW, TF-IDF, Word2Vec y BERT; fusión de modelos</t>
+        </is>
+      </c>
+      <c r="V91" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W91" s="4" t="inlineStr">
+        <is>
+          <t>Partición 70/30; validación cruzada de 2 pliegues (intercambio de subconjuntos)</t>
+        </is>
+      </c>
+      <c r="X91" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y91" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z91" s="4" t="inlineStr"/>
+      <c r="AA91" s="4" t="inlineStr">
+        <is>
+          <t>Mejor configuración ≈0.91–0.92 (BERT + CNN); la fusión mejora 2.4 % la exactitud</t>
+        </is>
+      </c>
+      <c r="AB91" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Clasificadores tradicionales (NB, SVM, LR)</t>
+        </is>
+      </c>
+      <c r="AD91" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE91" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF91" s="4" t="inlineStr">
+        <is>
+          <t>Pocos requerimientos etiquetados disponibles</t>
+        </is>
+      </c>
+      <c r="AG91" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH91" s="4" t="inlineStr">
+        <is>
+          <t>Prueba de Wilcoxon para comparar configuraciones. No precisa si el remuestreo se aplica solo al entrenamiento.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -6525,8 +8286,16 @@
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="4" t="n"/>
-      <c r="K93" s="4" t="n"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>CE2</t>
+        </is>
+      </c>
       <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
@@ -6549,7 +8318,11 @@
       <c r="AE93" s="4" t="n"/>
       <c r="AF93" s="4" t="n"/>
       <c r="AG93" s="4" t="n"/>
-      <c r="AH93" s="4" t="n"/>
+      <c r="AH93" s="4" t="inlineStr">
+        <is>
+          <t>Clasificación multietiqueta de 377 requerimientos industriales en taxonomías jerárquicas de dominio (1968 etiquetas, 6 espacios de salida) para trazabilidad; las clases no son tipos de requerimiento. Mismo grupo y tarea que el estudio 181.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -6833,31 +8606,123 @@
           <t>PROMISE; PROMISE_exp</t>
         </is>
       </c>
-      <c r="J98" s="4" t="n"/>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K98" s="4" t="n"/>
-      <c r="L98" s="4" t="n"/>
-      <c r="M98" s="4" t="n"/>
-      <c r="N98" s="4" t="n"/>
-      <c r="O98" s="4" t="n"/>
-      <c r="P98" s="4" t="n"/>
-      <c r="Q98" s="4" t="n"/>
-      <c r="R98" s="4" t="n"/>
-      <c r="S98" s="4" t="n"/>
-      <c r="T98" s="4" t="n"/>
-      <c r="U98" s="4" t="n"/>
-      <c r="V98" s="4" t="n"/>
-      <c r="W98" s="4" t="n"/>
-      <c r="X98" s="4" t="n"/>
-      <c r="Y98" s="4" t="n"/>
-      <c r="Z98" s="4" t="n"/>
-      <c r="AA98" s="4" t="n"/>
-      <c r="AB98" s="4" t="n"/>
-      <c r="AC98" s="4" t="n"/>
-      <c r="AD98" s="4" t="n"/>
-      <c r="AE98" s="4" t="n"/>
-      <c r="AF98" s="4" t="n"/>
-      <c r="AG98" s="4" t="n"/>
-      <c r="AH98" s="4" t="n"/>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR; PROMISE_exp</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (625) y PROMISE_exp (969)</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>Jerárquica</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>Nivel 1: FR/NFR; nivel 2: subclases de NFR</t>
+        </is>
+      </c>
+      <c r="R98" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S98" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna; F1 macro como métrica principal</t>
+        </is>
+      </c>
+      <c r="T98" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U98" s="4" t="inlineStr">
+        <is>
+          <t>BERT, SBERT, RoBERTa, NoRBERT, DeBERTa, XLNet; híbridos RoBERTa–DeBERTa y BERT–XLNet</t>
+        </is>
+      </c>
+      <c r="V98" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W98" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada</t>
+        </is>
+      </c>
+      <c r="X98" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y98" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1 por clase y macro; matrices de confusión</t>
+        </is>
+      </c>
+      <c r="Z98" s="4" t="inlineStr">
+        <is>
+          <t>BERT 0.34 (PROMISE) y 0.44 (PROMISE_exp); RoBERTa 0.55 (PROMISE_exp); híbrido RoBERTa–DeBERTa 0.63 (PROMISE)</t>
+        </is>
+      </c>
+      <c r="AA98" s="4" t="inlineStr"/>
+      <c r="AB98" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas; no detallado en el texto revisado</t>
+        </is>
+      </c>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>Modelos individuales frente a híbridos</t>
+        </is>
+      </c>
+      <c r="AD98" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE98" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF98" s="4" t="inlineStr">
+        <is>
+          <t>Desbalance de clases; tamaño de los conjuntos; variabilidad del ajuste fino</t>
+        </is>
+      </c>
+      <c r="AG98" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR5</t>
+        </is>
+      </c>
+      <c r="AH98" s="4" t="inlineStr">
+        <is>
+          <t>Evidencia clave: BERT ajustado sin tratamiento del desbalance obtiene F1 macro de 0.34–0.44 en la tarea multiclase, en línea con la línea base de TAOS (0.44). Código y datos en GitHub y Zenodo (10.5281/zenodo.15459346).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -7385,8 +9250,16 @@
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>CE2</t>
+        </is>
+      </c>
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
@@ -7409,7 +9282,11 @@
       <c r="AE107" s="4" t="n"/>
       <c r="AF107" s="4" t="n"/>
       <c r="AG107" s="4" t="n"/>
-      <c r="AH107" s="4" t="n"/>
+      <c r="AH107" s="4" t="inlineStr">
+        <is>
+          <t>Synthline genera datos sintéticos para clasificar DEFECTOS de especificación (ambiguo, no atómico, directivo, etc.; 131 requerimientos, 6 clases), no tipos de requerimiento. Útil como antecedente de generación con LLM (GPT-4o, DeepSeek-V3), no para la síntesis.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -7565,31 +9442,127 @@
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr"/>
-      <c r="J110" s="4" t="n"/>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K110" s="4" t="n"/>
-      <c r="L110" s="4" t="n"/>
-      <c r="M110" s="4" t="n"/>
-      <c r="N110" s="4" t="n"/>
-      <c r="O110" s="4" t="n"/>
-      <c r="P110" s="4" t="n"/>
-      <c r="Q110" s="4" t="n"/>
-      <c r="R110" s="4" t="n"/>
-      <c r="S110" s="4" t="n"/>
-      <c r="T110" s="4" t="n"/>
-      <c r="U110" s="4" t="n"/>
-      <c r="V110" s="4" t="n"/>
-      <c r="W110" s="4" t="n"/>
-      <c r="X110" s="4" t="n"/>
-      <c r="Y110" s="4" t="n"/>
-      <c r="Z110" s="4" t="n"/>
-      <c r="AA110" s="4" t="n"/>
-      <c r="AB110" s="4" t="n"/>
-      <c r="AC110" s="4" t="n"/>
-      <c r="AD110" s="4" t="n"/>
-      <c r="AE110" s="4" t="n"/>
-      <c r="AF110" s="4" t="n"/>
-      <c r="AG110" s="4" t="n"/>
-      <c r="AH110" s="4" t="n"/>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE original; PROMISE reetiquetado según ISO/IEC 25010 (por los autores); PURE</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>625 (PROMISE); PURE</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR; multiclase de NFR (original y reetiquetada)</t>
+        </is>
+      </c>
+      <c r="R110" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S110" s="4" t="inlineStr">
+        <is>
+          <t>Selección estratificada de ejemplos few-shot</t>
+        </is>
+      </c>
+      <c r="T110" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U110" s="4" t="inlineStr">
+        <is>
+          <t>GPT-4o, GPT-3.5-turbo, DeepSeek-V3, Gemma-3, LLaMA-3.1, LLaMA-3.2, Mistral</t>
+        </is>
+      </c>
+      <c r="V110" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador few-shot</t>
+        </is>
+      </c>
+      <c r="W110" s="4" t="inlineStr">
+        <is>
+          <t>Partición 80/20; ejemplos few-shot elegidos al azar, por embeddings o por TF-IDF, en cantidad creciente</t>
+        </is>
+      </c>
+      <c r="X110" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y110" s="4" t="inlineStr">
+        <is>
+          <t>F1 ponderado y F1 macro; precisión y exhaustividad por clase</t>
+        </is>
+      </c>
+      <c r="Z110" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE original multiclase: 0.60–0.80 según el modelo</t>
+        </is>
+      </c>
+      <c r="AA110" s="4" t="inlineStr">
+        <is>
+          <t>Binaria: LLaMA-3.1-8B 0.95 (supera el estado del arte en 1 punto); multiclase original: DeepSeek-V3 0.92; reetiquetado: GPT-4o 0.905</t>
+        </is>
+      </c>
+      <c r="AB110" s="4" t="inlineStr">
+        <is>
+          <t>El F1 macro es menor que el ponderado en todos los modelos</t>
+        </is>
+      </c>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Estado del arte en PROMISE y modelos ajustados</t>
+        </is>
+      </c>
+      <c r="AD110" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE110" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="AF110" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AG110" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR3, PR5</t>
+        </is>
+      </c>
+      <c r="AH110" s="4" t="inlineStr">
+        <is>
+          <t>Sobre-prompting: más ejemplos pueden empeorar el resultado. Los autores concluyen que los LLM se concentran en las clases dominantes y descuidan las menos frecuentes (macro &lt; ponderado).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -7629,31 +9602,123 @@
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="4" t="n"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="n"/>
-      <c r="L111" s="4" t="n"/>
-      <c r="M111" s="4" t="n"/>
-      <c r="N111" s="4" t="n"/>
-      <c r="O111" s="4" t="n"/>
-      <c r="P111" s="4" t="n"/>
-      <c r="Q111" s="4" t="n"/>
-      <c r="R111" s="4" t="n"/>
-      <c r="S111" s="4" t="n"/>
-      <c r="T111" s="4" t="n"/>
-      <c r="U111" s="4" t="n"/>
-      <c r="V111" s="4" t="n"/>
-      <c r="W111" s="4" t="n"/>
-      <c r="X111" s="4" t="n"/>
-      <c r="Y111" s="4" t="n"/>
-      <c r="Z111" s="4" t="n"/>
-      <c r="AA111" s="4" t="n"/>
-      <c r="AB111" s="4" t="n"/>
-      <c r="AC111" s="4" t="n"/>
-      <c r="AD111" s="4" t="n"/>
-      <c r="AE111" s="4" t="n"/>
-      <c r="AF111" s="4" t="n"/>
-      <c r="AG111" s="4" t="n"/>
-      <c r="AH111" s="4" t="n"/>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (solo FR, 6 clases); conjunto propietario de 600 FR (6 clases)</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>600 (propietario) y FR de PROMISE</t>
+        </is>
+      </c>
+      <c r="P111" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="inlineStr">
+        <is>
+          <t>6 (subcategorías de FR)</t>
+        </is>
+      </c>
+      <c r="R111" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S111" s="4" t="inlineStr">
+        <is>
+          <t>Sobremuestreo modificado y ensamble ponderado por exactitud por clase</t>
+        </is>
+      </c>
+      <c r="T111" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="U111" s="4" t="inlineStr">
+        <is>
+          <t>Ensamble de BERT, DistilBERT y RoBERTa con fusión por atención; comparado con CNN, LSTM, BiLSTM, GRU y SEBERT</t>
+        </is>
+      </c>
+      <c r="V111" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W111" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada de 5 pliegues; 10 ejecuciones para las pruebas</t>
+        </is>
+      </c>
+      <c r="X111" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y111" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, F1, kappa de Cohen, G-mean, MCC; F1 por clase</t>
+        </is>
+      </c>
+      <c r="Z111" s="4" t="inlineStr"/>
+      <c r="AA111" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE: F1 0.95, MCC 0.94; propietario: F1 0.94, MCC 0.94 (no especifica el promedio del F1)</t>
+        </is>
+      </c>
+      <c r="AB111" s="4" t="inlineStr">
+        <is>
+          <t>F1 por clase reportado; clases 'definición' y 'restricción de atributo' con 6 y 7 instancias</t>
+        </is>
+      </c>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>BERT, DistilBERT y RoBERTa individuales; CNN, LSTM, BiLSTM, GRU; SEBERT</t>
+        </is>
+      </c>
+      <c r="AD111" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE111" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF111" s="4" t="inlineStr">
+        <is>
+          <t>Tamaño de los conjuntos; desbalance en PROMISE (clases con 6 y 7 instancias); posible sesgo de selección en la partición</t>
+        </is>
+      </c>
+      <c r="AG111" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH111" s="4" t="inlineStr">
+        <is>
+          <t>Clasifica subcategorías de FR, no de NFR. Prueba t pareada en 10 ejecuciones (p &lt; 0.001). No precisa si el sobremuestreo se hizo antes de la validación cruzada.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -8453,31 +10518,123 @@
           <t>PURE</t>
         </is>
       </c>
-      <c r="J124" s="4" t="n"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K124" s="4" t="n"/>
-      <c r="L124" s="4" t="n"/>
-      <c r="M124" s="4" t="n"/>
-      <c r="N124" s="4" t="n"/>
-      <c r="O124" s="4" t="n"/>
-      <c r="P124" s="4" t="n"/>
-      <c r="Q124" s="4" t="n"/>
-      <c r="R124" s="4" t="n"/>
-      <c r="S124" s="4" t="n"/>
-      <c r="T124" s="4" t="n"/>
-      <c r="U124" s="4" t="n"/>
-      <c r="V124" s="4" t="n"/>
-      <c r="W124" s="4" t="n"/>
-      <c r="X124" s="4" t="n"/>
-      <c r="Y124" s="4" t="n"/>
-      <c r="Z124" s="4" t="n"/>
-      <c r="AA124" s="4" t="n"/>
-      <c r="AB124" s="4" t="n"/>
-      <c r="AC124" s="4" t="n"/>
-      <c r="AD124" s="4" t="n"/>
-      <c r="AE124" s="4" t="n"/>
-      <c r="AF124" s="4" t="n"/>
-      <c r="AG124" s="4" t="n"/>
-      <c r="AH124" s="4" t="n"/>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>PURE (conjunto construido por los autores)</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>4661 (2617 FR, 2044 NFR)</t>
+        </is>
+      </c>
+      <c r="P124" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R124" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S124" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T124" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U124" s="4" t="inlineStr">
+        <is>
+          <t>CNN, LSTM, BiLSTM, GRU, BiGRU con embeddings de Keras y GloVe; votación dura y blanda</t>
+        </is>
+      </c>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W124" s="4" t="inlineStr">
+        <is>
+          <t>10 ejecuciones con media y desviación estándar; la partición no se precisa en el texto revisado</t>
+        </is>
+      </c>
+      <c r="X124" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y124" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, F1 (con desviación estándar)</t>
+        </is>
+      </c>
+      <c r="Z124" s="4" t="inlineStr"/>
+      <c r="AA124" s="4" t="inlineStr">
+        <is>
+          <t>BiLSTM, primero entre los modelos DL; la votación mejora la exactitud</t>
+        </is>
+      </c>
+      <c r="AB124" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Comparación entre modelos DL</t>
+        </is>
+      </c>
+      <c r="AD124" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE124" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF124" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG124" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH124" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto grande derivado de PURE, útil como alternativa a PROMISE en la tarea binaria.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -8765,31 +10922,123 @@
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr"/>
-      <c r="J129" s="4" t="n"/>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K129" s="4" t="n"/>
-      <c r="L129" s="4" t="n"/>
-      <c r="M129" s="4" t="n"/>
-      <c r="N129" s="4" t="n"/>
-      <c r="O129" s="4" t="n"/>
-      <c r="P129" s="4" t="n"/>
-      <c r="Q129" s="4" t="n"/>
-      <c r="R129" s="4" t="n"/>
-      <c r="S129" s="4" t="n"/>
-      <c r="T129" s="4" t="n"/>
-      <c r="U129" s="4" t="n"/>
-      <c r="V129" s="4" t="n"/>
-      <c r="W129" s="4" t="n"/>
-      <c r="X129" s="4" t="n"/>
-      <c r="Y129" s="4" t="n"/>
-      <c r="Z129" s="4" t="n"/>
-      <c r="AA129" s="4" t="n"/>
-      <c r="AB129" s="4" t="n"/>
-      <c r="AC129" s="4" t="n"/>
-      <c r="AD129" s="4" t="n"/>
-      <c r="AE129" s="4" t="n"/>
-      <c r="AF129" s="4" t="n"/>
-      <c r="AG129" s="4" t="n"/>
-      <c r="AH129" s="4" t="n"/>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>Issues/GitHub</t>
+        </is>
+      </c>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>GitReq: 6302 issues validados por expertos (de 55 588 candidatos en 4080 repositorios)</t>
+        </is>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="P129" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="inlineStr">
+        <is>
+          <t>8 (7 categorías ISO/IEC 25010 y FR)</t>
+        </is>
+      </c>
+      <c r="R129" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S129" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (recomienda estratificación, pesos o sobremuestreo para el entrenamiento supervisado)</t>
+        </is>
+      </c>
+      <c r="T129" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U129" s="4" t="inlineStr">
+        <is>
+          <t>GPT-5.2, LLaMA 3 70B, Mistral 7B y Gemma 3 4B en zero-shot</t>
+        </is>
+      </c>
+      <c r="V129" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W129" s="4" t="inlineStr">
+        <is>
+          <t>Zero-shot sobre el conjunto completo como línea base del benchmark</t>
+        </is>
+      </c>
+      <c r="X129" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y129" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase; F1 macro</t>
+        </is>
+      </c>
+      <c r="Z129" s="4" t="inlineStr">
+        <is>
+          <t>GPT-5.2 0.641 (el mejor de los cuatro LLM)</t>
+        </is>
+      </c>
+      <c r="AA129" s="4" t="inlineStr"/>
+      <c r="AB129" s="4" t="inlineStr">
+        <is>
+          <t>Mantenibilidad 0.145–0.518 según el modelo; escalabilidad y mantenibilidad son las clases menores (157 y 144)</t>
+        </is>
+      </c>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Comparación entre cuatro LLM</t>
+        </is>
+      </c>
+      <c r="AD129" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE129" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF129" s="4" t="inlineStr">
+        <is>
+          <t>Solo issues en inglés; posible falta de representatividad industrial</t>
+        </is>
+      </c>
+      <c r="AG129" s="4" t="inlineStr">
+        <is>
+          <t>PR3, PR4</t>
+        </is>
+      </c>
+      <c r="AH129" s="4" t="inlineStr">
+        <is>
+          <t>Preprint en arXiv. Elimina duplicados con similitud TF-IDF ≥ 0.85 y anotación experta con Fleiss κ = 0.72. Datos en figshare (10.6084/m9.figshare.31669477). Fuente directa para la ampliación con GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
@@ -8897,31 +11146,127 @@
           <t>PROMISE_exp</t>
         </is>
       </c>
-      <c r="J131" s="4" t="n"/>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K131" s="4" t="n"/>
-      <c r="L131" s="4" t="n"/>
-      <c r="M131" s="4" t="n"/>
-      <c r="N131" s="4" t="n"/>
-      <c r="O131" s="4" t="n"/>
-      <c r="P131" s="4" t="n"/>
-      <c r="Q131" s="4" t="n"/>
-      <c r="R131" s="4" t="n"/>
-      <c r="S131" s="4" t="n"/>
-      <c r="T131" s="4" t="n"/>
-      <c r="U131" s="4" t="n"/>
-      <c r="V131" s="4" t="n"/>
-      <c r="W131" s="4" t="n"/>
-      <c r="X131" s="4" t="n"/>
-      <c r="Y131" s="4" t="n"/>
-      <c r="Z131" s="4" t="n"/>
-      <c r="AA131" s="4" t="n"/>
-      <c r="AB131" s="4" t="n"/>
-      <c r="AC131" s="4" t="n"/>
-      <c r="AD131" s="4" t="n"/>
-      <c r="AE131" s="4" t="n"/>
-      <c r="AF131" s="4" t="n"/>
-      <c r="AG131" s="4" t="n"/>
-      <c r="AH131" s="4" t="n"/>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE_exp</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>969 (444 FR, 525 NFR)</t>
+        </is>
+      </c>
+      <c r="P131" s="4" t="inlineStr">
+        <is>
+          <t>Jerárquica</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="inlineStr">
+        <is>
+          <t>Nivel 1: FR/NFR; nivel 2: 12 categorías de NFR</t>
+        </is>
+      </c>
+      <c r="R131" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S131" s="4" t="inlineStr">
+        <is>
+          <t>Pesos de clase en ML; Focal Loss en los modelos neuronales</t>
+        </is>
+      </c>
+      <c r="T131" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U131" s="4" t="inlineStr">
+        <is>
+          <t>SVM lineal, regresión logística, random forest, NB; CNN, BiLSTM; BERT y variantes adaptadas al dominio</t>
+        </is>
+      </c>
+      <c r="V131" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W131" s="4" t="inlineStr">
+        <is>
+          <t>Partición entrenamiento/prueba con búsqueda en malla de hiperparámetros (proporción no precisada en el texto revisado)</t>
+        </is>
+      </c>
+      <c r="X131" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y131" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, especificidad, F1 macro y ponderado, F1 por clase</t>
+        </is>
+      </c>
+      <c r="Z131" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR: RL 0.66, SVM 0.65, CNN 0.49; binaria: CNN 0.85</t>
+        </is>
+      </c>
+      <c r="AA131" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR: RL 0.72, SVM 0.71</t>
+        </is>
+      </c>
+      <c r="AB131" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas</t>
+        </is>
+      </c>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Comparación entre ML, DL y transformers</t>
+        </is>
+      </c>
+      <c r="AD131" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE131" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF131" s="4" t="inlineStr">
+        <is>
+          <t>Desbalance y bajo rendimiento en las subclases raras de NFR</t>
+        </is>
+      </c>
+      <c r="AG131" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH131" s="4" t="inlineStr">
+        <is>
+          <t>Caracteriza el desbalance de PROMISE_exp. Recomienda explícitamente explorar aumentación de datos y optimización sensible al desbalance para las clases raras.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
@@ -9473,8 +11818,16 @@
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr"/>
-      <c r="J140" s="4" t="n"/>
-      <c r="K140" s="4" t="n"/>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>CE3</t>
+        </is>
+      </c>
       <c r="L140" s="4" t="n"/>
       <c r="M140" s="4" t="n"/>
       <c r="N140" s="4" t="n"/>
@@ -9497,7 +11850,11 @@
       <c r="AE140" s="4" t="n"/>
       <c r="AF140" s="4" t="n"/>
       <c r="AG140" s="4" t="n"/>
-      <c r="AH140" s="4" t="n"/>
+      <c r="AH140" s="4" t="inlineStr">
+        <is>
+          <t>Demostración de una herramienta (RITA) que integra técnicas con LLM evaluadas en trabajos previos; no reporta una evaluación empírica nueva.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -9841,31 +12198,123 @@
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr"/>
-      <c r="J146" s="4" t="n"/>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K146" s="4" t="n"/>
-      <c r="L146" s="4" t="n"/>
-      <c r="M146" s="4" t="n"/>
-      <c r="N146" s="4" t="n"/>
-      <c r="O146" s="4" t="n"/>
-      <c r="P146" s="4" t="n"/>
-      <c r="Q146" s="4" t="n"/>
-      <c r="R146" s="4" t="n"/>
-      <c r="S146" s="4" t="n"/>
-      <c r="T146" s="4" t="n"/>
-      <c r="U146" s="4" t="n"/>
-      <c r="V146" s="4" t="n"/>
-      <c r="W146" s="4" t="n"/>
-      <c r="X146" s="4" t="n"/>
-      <c r="Y146" s="4" t="n"/>
-      <c r="Z146" s="4" t="n"/>
-      <c r="AA146" s="4" t="n"/>
-      <c r="AB146" s="4" t="n"/>
-      <c r="AC146" s="4" t="n"/>
-      <c r="AD146" s="4" t="n"/>
-      <c r="AE146" s="4" t="n"/>
-      <c r="AF146" s="4" t="n"/>
-      <c r="AG146" s="4" t="n"/>
-      <c r="AH146" s="4" t="n"/>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>300 reseñas de tres apps etiquetadas por dos expertos en usabilidad</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>Inglés y alemán</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P146" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr">
+        <is>
+          <t>2 (relevante o no para la usabilidad)</t>
+        </is>
+      </c>
+      <c r="R146" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S146" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T146" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U146" s="4" t="inlineStr">
+        <is>
+          <t>GPT-4.1 con prompt refinado en dos iteraciones</t>
+        </is>
+      </c>
+      <c r="V146" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W146" s="4" t="inlineStr">
+        <is>
+          <t>Comparación con la etiqueta final de los expertos, por app</t>
+        </is>
+      </c>
+      <c r="X146" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="Y146" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, F1 y kappa de Cohen</t>
+        </is>
+      </c>
+      <c r="Z146" s="4" t="inlineStr"/>
+      <c r="AA146" s="4" t="inlineStr">
+        <is>
+          <t>F1 de la clase positiva: 0.82, 0.82 y ≈0.78 en las tres apps</t>
+        </is>
+      </c>
+      <c r="AB146" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Evaluadores humanos expertos</t>
+        </is>
+      </c>
+      <c r="AD146" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE146" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF146" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG146" s="4" t="inlineStr">
+        <is>
+          <t>PR3</t>
+        </is>
+      </c>
+      <c r="AH146" s="4" t="inlineStr">
+        <is>
+          <t>Preprint en arXiv. El LLM es más permisivo que los expertos (más falsos positivos); el resultado depende mucho del prompt.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AH146"/>
@@ -10043,20 +12492,60 @@
           <t>Automatically classifying requirements from app stores: A preliminary study</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L3" s="6">
         <f>IF(COUNTA(D3:K3)=0,"",COUNTIF(D3:K3,"Sí")+0.5*COUNTIF(D3:K3,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M3" s="6" t="n"/>
-      <c r="N3" s="6" t="n"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>QA4 = 0: solo exactitud.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -10124,20 +12613,60 @@
           <t>Study of various classifiers for identification and classification of non-functional requirements</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L6" s="6">
         <f>IF(COUNTA(D6:K6)=0,"",COUNTIF(D6:K6,"Sí")+0.5*COUNTIF(D6:K6,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 derivado de P y R promediados por clase. QA6 parcial: reporta varianza.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -10151,20 +12680,60 @@
           <t>An automated approach for identification of non-functional requirements using Word2Vec model</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L7" s="6">
         <f>IF(COUNTA(D7:K7)=0,"",COUNTIF(D7:K7,"Sí")+0.5*COUNTIF(D7:K7,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>QA4 completo: tabla por clase. Sin entrenamiento, por lo que no hay partición que evaluar.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -10205,20 +12774,60 @@
           <t>NoRBERT: Transfer Learning for Requirements Classification</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L9" s="6">
         <f>IF(COUNTA(D9:K9)=0,"",COUNTIF(D9:K9,"Sí")+0.5*COUNTIF(D9:K9,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>QA3: protocolo con partición estratificada y por proyecto; remuestreo solo en entrenamiento. QA4 parcial: F1 por clase y ponderado, sin macro explícito.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -10502,20 +13111,60 @@
           <t>Automatic Requirements Classification Based on Graph Attention Network</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L20" s="6">
         <f>IF(COUNTA(D20:K20)=0,"",COUNTIF(D20:K20,"Sí")+0.5*COUNTIF(D20:K20,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>QA3: usa el conjunto reetiquetado y validación por proyecto. QA4 parcial: solo F1 ponderado.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -10799,20 +13448,60 @@
           <t>A machine learning approach for hierarchical classification of software requirements</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L31" s="6">
         <f>IF(COUNTA(D31:K31)=0,"",COUNTIF(D31:K31,"Sí")+0.5*COUNTIF(D31:K31,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M31" s="6" t="n"/>
-      <c r="N31" s="6" t="n"/>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>QA4 completo: macro, micro y por clase. Sin prueba estadística.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -11069,20 +13758,60 @@
           <t>Zero-shot learning for requirements classification: An exploratory study</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L41" s="6">
         <f>IF(COUNTA(D41:K41)=0,"",COUNTIF(D41:K41,"Sí")+0.5*COUNTIF(D41:K41,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M41" s="6" t="n"/>
-      <c r="N41" s="6" t="n"/>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 ponderado y por clase, sin macro.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -11285,20 +14014,60 @@
           <t>Hybrid SVM-Bidirectional Long Short-Term Memory Model for Fine-Grained Software Requirement Classification</t>
         </is>
       </c>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L49" s="6">
         <f>IF(COUNTA(D49:K49)=0,"",COUNTIF(D49:K49,"Sí")+0.5*COUNTIF(D49:K49,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M49" s="6" t="n"/>
-      <c r="N49" s="6" t="n"/>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: remuestreo previo a la partición (riesgo de fuga). QA6 parcial: resultados por pliegue.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -11312,20 +14081,60 @@
           <t>Lessons from the Use of Natural Language Inference (NLI) in Requirements Engineering Tasks</t>
         </is>
       </c>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
-      <c r="J50" s="7" t="n"/>
-      <c r="K50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L50" s="6">
         <f>IF(COUNTA(D50:K50)=0,"",COUNTIF(D50:K50,"Sí")+0.5*COUNTIF(D50:K50,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="6" t="n"/>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 por clase, sin promedio macro explícito.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -11339,20 +14148,60 @@
           <t>MLR-predictor: a versatile and efficient computational framework for multi-label requirements classification</t>
         </is>
       </c>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L51" s="6">
         <f>IF(COUNTA(D51:K51)=0,"",COUNTIF(D51:K51,"Sí")+0.5*COUNTIF(D51:K51,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M51" s="6" t="n"/>
-      <c r="N51" s="6" t="n"/>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: validación cruzada descrita, sin fuga discutida.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -11609,20 +14458,60 @@
           <t>Analyzing the Impact of Machine Learning Algorithms on Software Requirements Classification</t>
         </is>
       </c>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L61" s="6">
         <f>IF(COUNTA(D61:K61)=0,"",COUNTIF(D61:K61,"Sí")+0.5*COUNTIF(D61:K61,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M61" s="6" t="n"/>
-      <c r="N61" s="6" t="n"/>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>QA4 = 0: solo exactitud, precisión y exhaustividad globales.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -11636,20 +14525,60 @@
           <t>Are prompts all you need? Evaluating prompt-based Large Language Models (LLM)s for software requirements classification</t>
         </is>
       </c>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="K62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L62" s="6">
         <f>IF(COUNTA(D62:K62)=0,"",COUNTIF(D62:K62,"Sí")+0.5*COUNTIF(D62:K62,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M62" s="6" t="n"/>
-      <c r="N62" s="6" t="n"/>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: partición estratificada descrita, sin control de duplicados. QA7 parcial: prompts y resultados en OSF, sin código de entrenamiento.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -11960,20 +14889,60 @@
           <t>Classification of Requirements from Software Requirement Specification Documents TAOS: A Novel TextAttack Oversampling Approach for Fine-Grained Classification of Software Requirements</t>
         </is>
       </c>
-      <c r="D74" s="7" t="n"/>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
-      <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-      <c r="J74" s="7" t="n"/>
-      <c r="K74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L74" s="6">
         <f>IF(COUNTA(D74:K74)=0,"",COUNTIF(D74:K74,"Sí")+0.5*COUNTIF(D74:K74,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M74" s="6" t="n"/>
-      <c r="N74" s="6" t="n"/>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: aumenta solo el entrenamiento, pero la partición tiene duplicados. QA5 parcial: solo compara con BERT sin aumentación.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -12014,20 +14983,60 @@
           <t>Classification of quality characteristics in online user feedback using linguistic analysis, crowdsourcing and LLMs</t>
         </is>
       </c>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-      <c r="K76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L76" s="6">
         <f>IF(COUNTA(D76:K76)=0,"",COUNTIF(D76:K76,"Sí")+0.5*COUNTIF(D76:K76,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M76" s="6" t="n"/>
-      <c r="N76" s="6" t="n"/>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: exactitud global con precisión y exhaustividad por clase, sin F1 macro.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -12230,20 +15239,60 @@
           <t>Exploring Zero-Shot App Review Classification with ChatGPT: Challenges and Potential</t>
         </is>
       </c>
-      <c r="D84" s="7" t="n"/>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="7" t="n"/>
-      <c r="G84" s="7" t="n"/>
-      <c r="H84" s="7" t="n"/>
-      <c r="I84" s="7" t="n"/>
-      <c r="J84" s="7" t="n"/>
-      <c r="K84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L84" s="6">
         <f>IF(COUNTA(D84:K84)=0,"",COUNTIF(D84:K84,"Sí")+0.5*COUNTIF(D84:K84,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M84" s="6" t="n"/>
-      <c r="N84" s="6" t="n"/>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>QA4: solo F1 micro.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -12284,20 +15333,60 @@
           <t>Generating Synthetic Nonfunctional Requirements using Large Language Models for Training Machine Learning Classifiers</t>
         </is>
       </c>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
-      <c r="K86" s="7" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L86" s="6">
         <f>IF(COUNTA(D86:K86)=0,"",COUNTIF(D86:K86,"Sí")+0.5*COUNTIF(D86:K86,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M86" s="6" t="n"/>
-      <c r="N86" s="6" t="n"/>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: protocolo descrito, sin precisar fuga entre real y sintético. QA4 parcial: solo F1 ponderado y por clase, sin macro.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -12311,20 +15400,60 @@
           <t>Generative language models potential for requirement engineering applications: insights into current strengths and limitations</t>
         </is>
       </c>
-      <c r="D87" s="7" t="n"/>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="7" t="n"/>
-      <c r="G87" s="7" t="n"/>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
-      <c r="J87" s="7" t="n"/>
-      <c r="K87" s="7" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L87" s="6">
         <f>IF(COUNTA(D87:K87)=0,"",COUNTIF(D87:K87,"Sí")+0.5*COUNTIF(D87:K87,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M87" s="6" t="n"/>
-      <c r="N87" s="6" t="n"/>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>QA2 parcial: las clases de PROMISE no se precisan. QA6 parcial: promedio de cinco particiones, sin pruebas.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -12392,20 +15521,60 @@
           <t>Hybrid Deep Learning Approach for Automating App Review Classification: Advancing Usability Metrics Classification with an Aspect-Based Sentiment Analysis Framework</t>
         </is>
       </c>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
-      <c r="I90" s="7" t="n"/>
-      <c r="J90" s="7" t="n"/>
-      <c r="K90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L90" s="6">
         <f>IF(COUNTA(D90:K90)=0,"",COUNTIF(D90:K90,"Sí")+0.5*COUNTIF(D90:K90,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M90" s="6" t="n"/>
-      <c r="N90" s="6" t="n"/>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>QA4: no reporta F1 macro ni por clase pese al sesgo de clases.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -12419,20 +15588,60 @@
           <t>Identifying Non-Functional Requirements From Unconstrained Documents Using Natural Language Processing and Machine Learning Approaches</t>
         </is>
       </c>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L91" s="6">
         <f>IF(COUNTA(D91:K91)=0,"",COUNTIF(D91:K91,"Sí")+0.5*COUNTIF(D91:K91,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M91" s="6" t="n"/>
-      <c r="N91" s="6" t="n"/>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>QA2 parcial: no precisa el número de requerimientos. QA4 parcial: F1 sin especificar el promedio.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -12608,20 +15817,60 @@
           <t>Multi-Level Software Requirements Classification: Assessing BERT Variants and their Hybrid Models</t>
         </is>
       </c>
-      <c r="D98" s="7" t="n"/>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-      <c r="J98" s="7" t="n"/>
-      <c r="K98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L98" s="6">
         <f>IF(COUNTA(D98:K98)=0,"",COUNTIF(D98:K98,"Sí")+0.5*COUNTIF(D98:K98,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M98" s="6" t="n"/>
-      <c r="N98" s="6" t="n"/>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>QA6 parcial: solo desviación entre modelos, sin pruebas.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -12932,20 +16181,60 @@
           <t>The Few-shot Dilemma: Over-prompting Large Language Models</t>
         </is>
       </c>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-      <c r="J110" s="7" t="n"/>
-      <c r="K110" s="7" t="n"/>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L110" s="6">
         <f>IF(COUNTA(D110:K110)=0,"",COUNTIF(D110:K110,"Sí")+0.5*COUNTIF(D110:K110,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M110" s="6" t="n"/>
-      <c r="N110" s="6" t="n"/>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>QA4 completo: reporta F1 macro y ponderado. Sin repositorio identificado.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -12959,20 +16248,60 @@
           <t>A Deep Learning Approach to Classifying Software Requirements: The Application of Transformer-Based Ensemble Learning and Attention-Based Fusion</t>
         </is>
       </c>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="n"/>
-      <c r="G111" s="7" t="n"/>
-      <c r="H111" s="7" t="n"/>
-      <c r="I111" s="7" t="n"/>
-      <c r="J111" s="7" t="n"/>
-      <c r="K111" s="7" t="n"/>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L111" s="6">
         <f>IF(COUNTA(D111:K111)=0,"",COUNTIF(D111:K111,"Sí")+0.5*COUNTIF(D111:K111,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M111" s="6" t="n"/>
-      <c r="N111" s="6" t="n"/>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: validación cruzada descrita, sin indicar si el sobremuestreo precede a la partición. QA7: sin código ni datos propietarios.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -13310,20 +16639,60 @@
           <t>Deep Learning Methods for Software Requirement Classification: A Performance Study on the Pure Dataset</t>
         </is>
       </c>
-      <c r="D124" s="7" t="n"/>
-      <c r="E124" s="7" t="n"/>
-      <c r="F124" s="7" t="n"/>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
-      <c r="J124" s="7" t="n"/>
-      <c r="K124" s="7" t="n"/>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L124" s="6">
         <f>IF(COUNTA(D124:K124)=0,"",COUNTIF(D124:K124,"Sí")+0.5*COUNTIF(D124:K124,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M124" s="6" t="n"/>
-      <c r="N124" s="6" t="n"/>
+      <c r="M124" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N124" s="6" t="inlineStr">
+        <is>
+          <t>QA6 parcial: reporta desviación estándar en 10 ejecuciones, sin pruebas.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
@@ -13445,20 +16814,60 @@
           <t>GitReq: A Gold Standard Dataset for Software Quality Requirements</t>
         </is>
       </c>
-      <c r="D129" s="7" t="n"/>
-      <c r="E129" s="7" t="n"/>
-      <c r="F129" s="7" t="n"/>
-      <c r="G129" s="7" t="n"/>
-      <c r="H129" s="7" t="n"/>
-      <c r="I129" s="7" t="n"/>
-      <c r="J129" s="7" t="n"/>
-      <c r="K129" s="7" t="n"/>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L129" s="6">
         <f>IF(COUNTA(D129:K129)=0,"",COUNTIF(D129:K129,"Sí")+0.5*COUNTIF(D129:K129,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M129" s="6" t="n"/>
-      <c r="N129" s="6" t="n"/>
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N129" s="6" t="inlineStr">
+        <is>
+          <t>QA5 parcial: solo compara LLM entre sí, sin modelo supervisado.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
@@ -13499,20 +16908,60 @@
           <t>Hierarchical Software Requirement Classification Using Transformer-Based Language Models</t>
         </is>
       </c>
-      <c r="D131" s="7" t="n"/>
-      <c r="E131" s="7" t="n"/>
-      <c r="F131" s="7" t="n"/>
-      <c r="G131" s="7" t="n"/>
-      <c r="H131" s="7" t="n"/>
-      <c r="I131" s="7" t="n"/>
-      <c r="J131" s="7" t="n"/>
-      <c r="K131" s="7" t="n"/>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L131" s="6">
         <f>IF(COUNTA(D131:K131)=0,"",COUNTIF(D131:K131,"Sí")+0.5*COUNTIF(D131:K131,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M131" s="6" t="n"/>
-      <c r="N131" s="6" t="n"/>
+      <c r="M131" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N131" s="6" t="inlineStr">
+        <is>
+          <t>QA5 parcial: compara modelos propios, sin referencia al estado del arte.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n">
@@ -13904,20 +17353,60 @@
           <t>User Reviews as a Source for Usability Requirements: A Precursor Study on Using Large Language Models</t>
         </is>
       </c>
-      <c r="D146" s="7" t="n"/>
-      <c r="E146" s="7" t="n"/>
-      <c r="F146" s="7" t="n"/>
-      <c r="G146" s="7" t="n"/>
-      <c r="H146" s="7" t="n"/>
-      <c r="I146" s="7" t="n"/>
-      <c r="J146" s="7" t="n"/>
-      <c r="K146" s="7" t="n"/>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L146" s="6">
         <f>IF(COUNTA(D146:K146)=0,"",COUNTIF(D146:K146,"Sí")+0.5*COUNTIF(D146:K146,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M146" s="6" t="n"/>
-      <c r="N146" s="6" t="n"/>
+      <c r="M146" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N146" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 de la clase positiva y kappa, sin macro.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L146">

--- a/RSL/formulario_extraccion_calidad.xlsx
+++ b/RSL/formulario_extraccion_calidad.xlsx
@@ -1050,31 +1050,123 @@
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="4" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
-      <c r="AA4" s="4" t="n"/>
-      <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="4" t="n"/>
-      <c r="AE4" s="4" t="n"/>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="n"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Issues/GitHub</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Solicitudes de usuarios de foros de tres proyectos de código abierto en SourceForge (KeePass, Mumble, WinMerge), 1000 por proyecto</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Tipos de requerimiento (funcional y atributos de calidad como usabilidad, fiabilidad, desempeño)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna de remuestreo; palabras clave por clase y aprendizaje activo</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>SVM, k-NN y NB (Weka) con palabras clave específicas y no específicas del proyecto; aprendizaje activo</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada de 5 pliegues por proyecto</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F-measure por clase y promedio</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>F-measure promedio por proyecto en tablas (≈0.71–0.80)</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>Por clase; los autores destacan un desempeño estable en las clases minoritarias</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador sin aprendizaje basado en número de palabras clave; rasgos de texto simples</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>Antecedente temprano de clasificación de texto de usuarios de proyectos de código abierto. Usa rasgos de palabras clave para mejorar las clases minoritarias en lugar de remuestrear.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2470,31 +2562,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="n"/>
-      <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
-      <c r="AA21" s="4" t="n"/>
-      <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n"/>
-      <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (625) y SOFTWARE NFR (ampliación propia de PROMISE con unas 200 oraciones por categoría)</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>625 y SOFTWARE NFR</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>11 en PROMISE; más categorías en SOFTWARE NFR</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>Construcción de un conjunto balanceado (≈200 oraciones por categoría)</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>NFRNet: BERT con enmascaramiento de N-gramas + Bi-LSTM; comparado con 17 métodos (TextCNN, TextRNN y otros)</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada de 10 pliegues sobre SOFTWARE NFR</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase; desviación estándar entre clases</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="AA21" s="4" t="inlineStr">
+        <is>
+          <t>Supera a 17 métodos; F1 ≈ 0.91 según lo citan otros estudios</t>
+        </is>
+      </c>
+      <c r="AB21" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas (conjunto balanceado)</t>
+        </is>
+      </c>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>17 métodos de ML y DL</t>
+        </is>
+      </c>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE21" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF21" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG21" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
+          <t>Evita el desbalance construyendo un conjunto nuevo balanceado; los datos están en Google Drive. El origen de las oraciones nuevas no se precisa en el texto revisado.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2534,31 +2718,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
-      <c r="T22" s="4" t="n"/>
-      <c r="U22" s="4" t="n"/>
-      <c r="V22" s="4" t="n"/>
-      <c r="W22" s="4" t="n"/>
-      <c r="X22" s="4" t="n"/>
-      <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="4" t="n"/>
-      <c r="AA22" s="4" t="n"/>
-      <c r="AB22" s="4" t="n"/>
-      <c r="AC22" s="4" t="n"/>
-      <c r="AD22" s="4" t="n"/>
-      <c r="AE22" s="4" t="n"/>
-      <c r="AF22" s="4" t="n"/>
-      <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="4" t="n"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625)</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>4 NFR frecuentes (O, PE, SE, US)</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna; restringe la tarea a las 4 clases frecuentes</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>BERT-CNN; comparado con BERT y enfoques previos</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 10 pliegues</t>
+        </is>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 ponderado</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="inlineStr"/>
+      <c r="AA22" s="4" t="inlineStr">
+        <is>
+          <t>0.85 en las 4 clases frecuentes</t>
+        </is>
+      </c>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>No aplica (excluye las clases raras)</t>
+        </is>
+      </c>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>BERT y NoRBERT</t>
+        </is>
+      </c>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF22" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG22" s="4" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
+          <t>Ponencia corta (Procedia). Evita el desbalance seleccionando las clases frecuentes.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -3442,31 +3718,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n"/>
-      <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n"/>
-      <c r="R35" s="4" t="n"/>
-      <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
-      <c r="U35" s="4" t="n"/>
-      <c r="V35" s="4" t="n"/>
-      <c r="W35" s="4" t="n"/>
-      <c r="X35" s="4" t="n"/>
-      <c r="Y35" s="4" t="n"/>
-      <c r="Z35" s="4" t="n"/>
-      <c r="AA35" s="4" t="n"/>
-      <c r="AB35" s="4" t="n"/>
-      <c r="AC35" s="4" t="n"/>
-      <c r="AD35" s="4" t="n"/>
-      <c r="AE35" s="4" t="n"/>
-      <c r="AF35" s="4" t="n"/>
-      <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="4" t="n"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (versión de Zenodo)</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR; 4 frecuentes; 4 frecuentes + 'otras'; 10 subclases de NFR</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>Agrupa las clases minoritarias en 'otras'; descarta el submuestreo por el tamaño del conjunto</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>BERT-BiCNN (BERT + BiLSTM + CNN); seis arquitecturas DL de referencia</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 10 pliegues</t>
+        </is>
+      </c>
+      <c r="X35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y35" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por tarea</t>
+        </is>
+      </c>
+      <c r="Z35" s="4" t="inlineStr"/>
+      <c r="AA35" s="4" t="inlineStr">
+        <is>
+          <t>Supera a seis modelos DL en las cuatro tareas; el desempeño baja con más clases</t>
+        </is>
+      </c>
+      <c r="AB35" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en la tarea de 10 clases</t>
+        </is>
+      </c>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Seis modelos DL recientes</t>
+        </is>
+      </c>
+      <c r="AD35" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE35" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF35" s="4" t="inlineStr">
+        <is>
+          <t>Amenazas a la validez; señala el desbalance y los conflictos de etiquetado</t>
+        </is>
+      </c>
+      <c r="AG35" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2</t>
+        </is>
+      </c>
+      <c r="AH35" s="4" t="inlineStr">
+        <is>
+          <t>Prueba t de Student (α = 0.05). Datos públicos (Zenodo); código no publicado.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -6314,31 +6682,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J72" s="4" t="n"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
-      <c r="O72" s="4" t="n"/>
-      <c r="P72" s="4" t="n"/>
-      <c r="Q72" s="4" t="n"/>
-      <c r="R72" s="4" t="n"/>
-      <c r="S72" s="4" t="n"/>
-      <c r="T72" s="4" t="n"/>
-      <c r="U72" s="4" t="n"/>
-      <c r="V72" s="4" t="n"/>
-      <c r="W72" s="4" t="n"/>
-      <c r="X72" s="4" t="n"/>
-      <c r="Y72" s="4" t="n"/>
-      <c r="Z72" s="4" t="n"/>
-      <c r="AA72" s="4" t="n"/>
-      <c r="AB72" s="4" t="n"/>
-      <c r="AC72" s="4" t="n"/>
-      <c r="AD72" s="4" t="n"/>
-      <c r="AE72" s="4" t="n"/>
-      <c r="AF72" s="4" t="n"/>
-      <c r="AG72" s="4" t="n"/>
-      <c r="AH72" s="4" t="n"/>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>SecReq: ePurse, CPN y GPS (tres especificaciones industriales); preentrenamiento con CWE, CVE y código</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>≈510 (SecReq)</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>2 (seguridad / no seguridad)</t>
+        </is>
+      </c>
+      <c r="R72" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U72" s="4" t="inlineStr">
+        <is>
+          <t>Embeddings + ML clásico con ensambles y grid search; BERT preentrenado con CWE/CVE y CodeBERT</t>
+        </is>
+      </c>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W72" s="4" t="inlineStr">
+        <is>
+          <t>10 pliegues dentro del dominio; entrenamiento y prueba en dominios distintos (hold-out entre proyectos)</t>
+        </is>
+      </c>
+      <c r="X72" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y72" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z72" s="4" t="inlineStr"/>
+      <c r="AA72" s="4" t="inlineStr">
+        <is>
+          <t>Entre dominios, F1 medio 0.78; CweCveCodeBERT mejora ≈3 puntos de F1 y ≈14 de precisión sobre el mejor previo</t>
+        </is>
+      </c>
+      <c r="AB72" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>Li y Chen; Mohamad et al. (SMOTE + RF); Munaiah et al.</t>
+        </is>
+      </c>
+      <c r="AD72" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE72" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF72" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG72" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR5</t>
+        </is>
+      </c>
+      <c r="AH72" s="4" t="inlineStr">
+        <is>
+          <t>Prueba de McNemar. La evaluación entre dominios evita que el mismo proyecto aparezca en entrenamiento y prueba. Paquete en Zenodo.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -6826,31 +7286,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J77" s="4" t="n"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K77" s="4" t="n"/>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
-      <c r="N77" s="4" t="n"/>
-      <c r="O77" s="4" t="n"/>
-      <c r="P77" s="4" t="n"/>
-      <c r="Q77" s="4" t="n"/>
-      <c r="R77" s="4" t="n"/>
-      <c r="S77" s="4" t="n"/>
-      <c r="T77" s="4" t="n"/>
-      <c r="U77" s="4" t="n"/>
-      <c r="V77" s="4" t="n"/>
-      <c r="W77" s="4" t="n"/>
-      <c r="X77" s="4" t="n"/>
-      <c r="Y77" s="4" t="n"/>
-      <c r="Z77" s="4" t="n"/>
-      <c r="AA77" s="4" t="n"/>
-      <c r="AB77" s="4" t="n"/>
-      <c r="AC77" s="4" t="n"/>
-      <c r="AD77" s="4" t="n"/>
-      <c r="AE77" s="4" t="n"/>
-      <c r="AF77" s="4" t="n"/>
-      <c r="AG77" s="4" t="n"/>
-      <c r="AH77" s="4" t="n"/>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto descrito como PROMISE (1615 requerimientos; 1521 tras limpiar)</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR y multiclase de NFR</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="S77" s="4" t="inlineStr">
+        <is>
+          <t>SMOTE y pesos de clase</t>
+        </is>
+      </c>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U77" s="4" t="inlineStr">
+        <is>
+          <t>SVM, RF, CNN, LSTM y BERT; despliegue híbrido nube–borde</t>
+        </is>
+      </c>
+      <c r="V77" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W77" s="4" t="inlineStr">
+        <is>
+          <t>SMOTE sobre el conjunto preprocesado y después partición estratificada 70/15/15</t>
+        </is>
+      </c>
+      <c r="X77" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y77" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z77" s="4" t="inlineStr"/>
+      <c r="AA77" s="4" t="inlineStr">
+        <is>
+          <t>BERT: 0.913 binaria y 0.892 multiclase</t>
+        </is>
+      </c>
+      <c r="AB77" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Modelos propios de ML y DL</t>
+        </is>
+      </c>
+      <c r="AD77" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE77" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF77" s="4" t="inlineStr">
+        <is>
+          <t>Especificidad de dominio de PROMISE</t>
+        </is>
+      </c>
+      <c r="AG77" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH77" s="4" t="inlineStr">
+        <is>
+          <t>El texto dice que se aplicó SMOTE y 'finalmente' se partió el conjunto: las muestras sintéticas pueden quedar en prueba (fuga). Elimina duplicados antes. El tamaño (1615) no coincide con PROMISE (625) ni con PROMISE_exp (969).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -8358,31 +8910,123 @@
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="4" t="n"/>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="n"/>
-      <c r="L94" s="4" t="n"/>
-      <c r="M94" s="4" t="n"/>
-      <c r="N94" s="4" t="n"/>
-      <c r="O94" s="4" t="n"/>
-      <c r="P94" s="4" t="n"/>
-      <c r="Q94" s="4" t="n"/>
-      <c r="R94" s="4" t="n"/>
-      <c r="S94" s="4" t="n"/>
-      <c r="T94" s="4" t="n"/>
-      <c r="U94" s="4" t="n"/>
-      <c r="V94" s="4" t="n"/>
-      <c r="W94" s="4" t="n"/>
-      <c r="X94" s="4" t="n"/>
-      <c r="Y94" s="4" t="n"/>
-      <c r="Z94" s="4" t="n"/>
-      <c r="AA94" s="4" t="n"/>
-      <c r="AB94" s="4" t="n"/>
-      <c r="AC94" s="4" t="n"/>
-      <c r="AD94" s="4" t="n"/>
-      <c r="AE94" s="4" t="n"/>
-      <c r="AF94" s="4" t="n"/>
-      <c r="AG94" s="4" t="n"/>
-      <c r="AH94" s="4" t="n"/>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>4732 requerimientos de nueve fuentes (PROMISE, PURE, Dronology, especificaciones en línea y tres proyectos privados)</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>4732</t>
+        </is>
+      </c>
+      <c r="P94" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>2 (casi balanceadas)</t>
+        </is>
+      </c>
+      <c r="R94" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S94" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (conjunto casi balanceado)</t>
+        </is>
+      </c>
+      <c r="T94" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U94" s="4" t="inlineStr">
+        <is>
+          <t>BERT, DistilBERT, DistilRoBERTa, ELECTRA, DeBERTaV3, RoBERTa, XLNet y ensamble por voto blando</t>
+        </is>
+      </c>
+      <c r="V94" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W94" s="4" t="inlineStr">
+        <is>
+          <t>No se describe la partición; se reporta el F1 por época (10 épocas)</t>
+        </is>
+      </c>
+      <c r="X94" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y94" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud y F1</t>
+        </is>
+      </c>
+      <c r="Z94" s="4" t="inlineStr"/>
+      <c r="AA94" s="4" t="inlineStr">
+        <is>
+          <t>Ensamble 0.925; DistilBERT 0.911</t>
+        </is>
+      </c>
+      <c r="AB94" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Modelos individuales</t>
+        </is>
+      </c>
+      <c r="AD94" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE94" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="AF94" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG94" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH94" s="4" t="inlineStr">
+        <is>
+          <t>Llama LLM a codificadores tipo BERT. Quita duplicados y requerimientos mal redactados. Reporta el mejor F1 entre épocas sin indicar sobre qué partición se eligió.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -10074,31 +10718,123 @@
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="4" t="n"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="n"/>
-      <c r="L117" s="4" t="n"/>
-      <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="n"/>
-      <c r="O117" s="4" t="n"/>
-      <c r="P117" s="4" t="n"/>
-      <c r="Q117" s="4" t="n"/>
-      <c r="R117" s="4" t="n"/>
-      <c r="S117" s="4" t="n"/>
-      <c r="T117" s="4" t="n"/>
-      <c r="U117" s="4" t="n"/>
-      <c r="V117" s="4" t="n"/>
-      <c r="W117" s="4" t="n"/>
-      <c r="X117" s="4" t="n"/>
-      <c r="Y117" s="4" t="n"/>
-      <c r="Z117" s="4" t="n"/>
-      <c r="AA117" s="4" t="n"/>
-      <c r="AB117" s="4" t="n"/>
-      <c r="AC117" s="4" t="n"/>
-      <c r="AD117" s="4" t="n"/>
-      <c r="AE117" s="4" t="n"/>
-      <c r="AF117" s="4" t="n"/>
-      <c r="AG117" s="4" t="n"/>
-      <c r="AH117" s="4" t="n"/>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M117" s="4" t="inlineStr">
+        <is>
+          <t>SecReq (623: 415 no seguridad, 208 seguridad)</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="P117" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="inlineStr">
+        <is>
+          <t>2 (seguridad / no seguridad)</t>
+        </is>
+      </c>
+      <c r="R117" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S117" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (lo propone como trabajo futuro)</t>
+        </is>
+      </c>
+      <c r="T117" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U117" s="4" t="inlineStr">
+        <is>
+          <t>BERT, RoBERTa, DistilBERT y DistilRoBERTa, ajuste completo y LoRA; explicabilidad con atención, gradientes integrados y SHAP</t>
+        </is>
+      </c>
+      <c r="V117" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W117" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada 80/10/10; 50 ensayos de optimización de hiperparámetros</t>
+        </is>
+      </c>
+      <c r="X117" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y117" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, F1 y matriz de confusión</t>
+        </is>
+      </c>
+      <c r="Z117" s="4" t="inlineStr"/>
+      <c r="AA117" s="4" t="inlineStr">
+        <is>
+          <t>RoBERTa 0.90 (ajuste completo); DistilBERT con LoRA 0.82</t>
+        </is>
+      </c>
+      <c r="AB117" s="4" t="inlineStr">
+        <is>
+          <t>Matriz de confusión</t>
+        </is>
+      </c>
+      <c r="AC117" s="4" t="inlineStr">
+        <is>
+          <t>Estudios previos sobre SecReq</t>
+        </is>
+      </c>
+      <c r="AD117" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE117" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF117" s="4" t="inlineStr">
+        <is>
+          <t>Tamaño y desbalance del conjunto</t>
+        </is>
+      </c>
+      <c r="AG117" s="4" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="AH117" s="4" t="inlineStr">
+        <is>
+          <t>Reconoce que el desbalance sesga hacia la clase mayoritaria y deja el remuestreo y la pérdida ponderada para trabajo futuro.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -10734,31 +11470,127 @@
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="4" t="n"/>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K126" s="4" t="n"/>
-      <c r="L126" s="4" t="n"/>
-      <c r="M126" s="4" t="n"/>
-      <c r="N126" s="4" t="n"/>
-      <c r="O126" s="4" t="n"/>
-      <c r="P126" s="4" t="n"/>
-      <c r="Q126" s="4" t="n"/>
-      <c r="R126" s="4" t="n"/>
-      <c r="S126" s="4" t="n"/>
-      <c r="T126" s="4" t="n"/>
-      <c r="U126" s="4" t="n"/>
-      <c r="V126" s="4" t="n"/>
-      <c r="W126" s="4" t="n"/>
-      <c r="X126" s="4" t="n"/>
-      <c r="Y126" s="4" t="n"/>
-      <c r="Z126" s="4" t="n"/>
-      <c r="AA126" s="4" t="n"/>
-      <c r="AB126" s="4" t="n"/>
-      <c r="AC126" s="4" t="n"/>
-      <c r="AD126" s="4" t="n"/>
-      <c r="AE126" s="4" t="n"/>
-      <c r="AF126" s="4" t="n"/>
-      <c r="AG126" s="4" t="n"/>
-      <c r="AH126" s="4" t="n"/>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>Combinación de MSHD-IAU, FR_NFR (Mendeley), CCHIT y PROMISE_exp (15 326 filas antes de quitar duplicados)</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>15 326 filas originales (menos tras deduplicar)</t>
+        </is>
+      </c>
+      <c r="P126" s="4" t="inlineStr">
+        <is>
+          <t>Jerárquica</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>Taxonomía de tres niveles FR/NFR alineada con ISO 25010 e ISO 29148; multietiqueta</t>
+        </is>
+      </c>
+      <c r="R126" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S126" s="4" t="inlineStr">
+        <is>
+          <t>Focal Loss como alternativa a la entropía cruzada</t>
+        </is>
+      </c>
+      <c r="T126" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U126" s="4" t="inlineStr">
+        <is>
+          <t>Transformer jerárquico con supervisión conjunta o escalonada</t>
+        </is>
+      </c>
+      <c r="V126" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W126" s="4" t="inlineStr">
+        <is>
+          <t>Partición aleatoria 70/20/10 frente a partición agrupada por longitud; varias semillas</t>
+        </is>
+      </c>
+      <c r="X126" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y126" s="4" t="inlineStr">
+        <is>
+          <t>F1 macro y micro por nivel; degradación por profundidad</t>
+        </is>
+      </c>
+      <c r="Z126" s="4" t="inlineStr">
+        <is>
+          <t>≈0.90 (nivel 1), 0.72 (nivel 2) y 0.55 (nivel 3)</t>
+        </is>
+      </c>
+      <c r="AA126" s="4" t="inlineStr">
+        <is>
+          <t>Micro-F1 &gt; 0.93 en el nivel 1 y 0.69 en el nivel 3</t>
+        </is>
+      </c>
+      <c r="AB126" s="4" t="inlineStr">
+        <is>
+          <t>Categorías hoja con &lt; 0.05 % de los ejemplos</t>
+        </is>
+      </c>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Supervisión conjunta frente a escalonada; comparación con la literatura</t>
+        </is>
+      </c>
+      <c r="AD126" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE126" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF126" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG126" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR5</t>
+        </is>
+      </c>
+      <c r="AH126" s="4" t="inlineStr">
+        <is>
+          <t>Wilcoxon con corrección de Holm–Bonferroni. Señala que la validación cruzada aleatoria domina la literatura y puede dar resultados optimistas, y que el desbalance y las pruebas estadísticas se tratan poco. La partición por longitud no fue significativamente mejor que la aleatoria.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -11310,31 +12142,123 @@
           <t>PROMISE_exp; PURE</t>
         </is>
       </c>
-      <c r="J132" s="4" t="n"/>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K132" s="4" t="n"/>
-      <c r="L132" s="4" t="n"/>
-      <c r="M132" s="4" t="n"/>
-      <c r="N132" s="4" t="n"/>
-      <c r="O132" s="4" t="n"/>
-      <c r="P132" s="4" t="n"/>
-      <c r="Q132" s="4" t="n"/>
-      <c r="R132" s="4" t="n"/>
-      <c r="S132" s="4" t="n"/>
-      <c r="T132" s="4" t="n"/>
-      <c r="U132" s="4" t="n"/>
-      <c r="V132" s="4" t="n"/>
-      <c r="W132" s="4" t="n"/>
-      <c r="X132" s="4" t="n"/>
-      <c r="Y132" s="4" t="n"/>
-      <c r="Z132" s="4" t="n"/>
-      <c r="AA132" s="4" t="n"/>
-      <c r="AB132" s="4" t="n"/>
-      <c r="AC132" s="4" t="n"/>
-      <c r="AD132" s="4" t="n"/>
-      <c r="AE132" s="4" t="n"/>
-      <c r="AF132" s="4" t="n"/>
-      <c r="AG132" s="4" t="n"/>
-      <c r="AH132" s="4" t="n"/>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>3072 requerimientos de PROMISE_exp, PURE y 20 especificaciones recopiladas; 3343 tras aumentar</t>
+        </is>
+      </c>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>3072 (3343 con aumentación)</t>
+        </is>
+      </c>
+      <c r="P132" s="4" t="inlineStr">
+        <is>
+          <t>Jerárquica</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>Nivel 1: FR/NFR; nivel 2: 4 subclases de FR y 3 de NFR</t>
+        </is>
+      </c>
+      <c r="R132" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S132" s="4" t="inlineStr">
+        <is>
+          <t>Aumentación contextual con BERT (sustitución) en las subclases minoritarias</t>
+        </is>
+      </c>
+      <c r="T132" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U132" s="4" t="inlineStr">
+        <is>
+          <t>BERT, RoBERTa, DistilBERT, ALBERT y modelo apilado LSTM-BERT-LSTM</t>
+        </is>
+      </c>
+      <c r="V132" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W132" s="4" t="inlineStr">
+        <is>
+          <t>Partición 80/10/10 tras aumentar y quitar duplicados; validación cruzada de 10 pliegues</t>
+        </is>
+      </c>
+      <c r="X132" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Y132" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z132" s="4" t="inlineStr"/>
+      <c r="AA132" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud del modelo propuesto 0.968 (nivel 1) y 0.831 (nivel 2); la aumentación mejora la exactitud 0.2–3.76 puntos y el F1 de nivel 2 de 0.789 a 0.820</t>
+        </is>
+      </c>
+      <c r="AB132" s="4" t="inlineStr">
+        <is>
+          <t>Análisis de errores por subclase</t>
+        </is>
+      </c>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>Transformers sin el modelo apilado; GPT-3.5 sin ajuste</t>
+        </is>
+      </c>
+      <c r="AD132" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE132" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="AF132" s="4" t="inlineStr">
+        <is>
+          <t>El desbalance persiste tras la aumentación</t>
+        </is>
+      </c>
+      <c r="AG132" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR4, PR5</t>
+        </is>
+      </c>
+      <c r="AH132" s="4" t="inlineStr">
+        <is>
+          <t>La aumentación se describe sobre el conjunto completo (3072 → 3343) antes de la partición; se quitan duplicados exactos, pero las variantes aumentadas de un requerimiento de prueba pueden quedar en entrenamiento. Prueba t frente a BERT. Compara también con GPT-3.5 (nivel 1: 0.892).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -11894,31 +12818,127 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J141" s="4" t="n"/>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K141" s="4" t="n"/>
-      <c r="L141" s="4" t="n"/>
-      <c r="M141" s="4" t="n"/>
-      <c r="N141" s="4" t="n"/>
-      <c r="O141" s="4" t="n"/>
-      <c r="P141" s="4" t="n"/>
-      <c r="Q141" s="4" t="n"/>
-      <c r="R141" s="4" t="n"/>
-      <c r="S141" s="4" t="n"/>
-      <c r="T141" s="4" t="n"/>
-      <c r="U141" s="4" t="n"/>
-      <c r="V141" s="4" t="n"/>
-      <c r="W141" s="4" t="n"/>
-      <c r="X141" s="4" t="n"/>
-      <c r="Y141" s="4" t="n"/>
-      <c r="Z141" s="4" t="n"/>
-      <c r="AA141" s="4" t="n"/>
-      <c r="AB141" s="4" t="n"/>
-      <c r="AC141" s="4" t="n"/>
-      <c r="AD141" s="4" t="n"/>
-      <c r="AE141" s="4" t="n"/>
-      <c r="AF141" s="4" t="n"/>
-      <c r="AG141" s="4" t="n"/>
-      <c r="AH141" s="4" t="n"/>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M141" s="4" t="inlineStr">
+        <is>
+          <t>Preentrenamiento con especificaciones (PURE y documentos industriales); ajuste con PROMISE NFR</t>
+        </is>
+      </c>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P141" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR; 5 frecuentes; 10 subclases de NFR (se excluye PO)</t>
+        </is>
+      </c>
+      <c r="R141" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S141" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (elimina la clase con un ejemplo)</t>
+        </is>
+      </c>
+      <c r="T141" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U141" s="4" t="inlineStr">
+        <is>
+          <t>RequiBERT (BERT preentrenado con requerimientos y tokenizador BPE); comparado con NoRBERT y otros</t>
+        </is>
+      </c>
+      <c r="V141" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W141" s="4" t="inlineStr">
+        <is>
+          <t>Partición entrenamiento/validación/prueba (proporción no precisada en el texto revisado)</t>
+        </is>
+      </c>
+      <c r="X141" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y141" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase y promedio</t>
+        </is>
+      </c>
+      <c r="Z141" s="4" t="inlineStr">
+        <is>
+          <t>0.85 promedio en las subclases de NFR (NoRBERT 0.81–0.82)</t>
+        </is>
+      </c>
+      <c r="AA141" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR 0.98–0.99; 5 clases frecuentes 0.95</t>
+        </is>
+      </c>
+      <c r="AB141" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas</t>
+        </is>
+      </c>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>NoRBERT, Kurtanović y Maalej, otros</t>
+        </is>
+      </c>
+      <c r="AD141" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE141" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="AF141" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AG141" s="4" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="AH141" s="4" t="inlineStr">
+        <is>
+          <t>Excluye PO porque un solo ejemplo no puede estar en entrenamiento y prueba. El preentrenamiento de dominio es la alternativa a la aumentación.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -12559,20 +13579,60 @@
           <t>Automatically classifying user requests in crowdsourcing requirements engineering</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="7" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L4" s="6">
         <f>IF(COUNTA(D4:K4)=0,"",COUNTIF(D4:K4,"Sí")+0.5*COUNTIF(D4:K4,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>QA4 completo: F-measure por clase.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -13178,20 +14238,60 @@
           <t>Automatically classifying non-functional requirements using deep neural network</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L21" s="6">
         <f>IF(COUNTA(D21:K21)=0,"",COUNTIF(D21:K21,"Sí")+0.5*COUNTIF(D21:K21,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 por clase sin promedio macro explícito. QA6 parcial: desviación estándar.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -13205,20 +14305,60 @@
           <t>BERT-CNN: Improving BERT for Requirements Classification using CNN</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L22" s="6">
         <f>IF(COUNTA(D22:K22)=0,"",COUNTIF(D22:K22,"Sí")+0.5*COUNTIF(D22:K22,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: solo F1 ponderado.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -13596,20 +14736,60 @@
           <t>Improving BERT model for requirements classification by bidirectional LSTM-CNN deep model</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L35" s="6">
         <f>IF(COUNTA(D35:K35)=0,"",COUNTIF(D35:K35,"Sí")+0.5*COUNTIF(D35:K35,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M35" s="6" t="n"/>
-      <c r="N35" s="6" t="n"/>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 sin promedio macro explícito.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -14835,20 +16015,60 @@
           <t>Beyond domain dependency in security requirements identification</t>
         </is>
       </c>
-      <c r="D72" s="7" t="n"/>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="n"/>
-      <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
-      <c r="J72" s="7" t="n"/>
-      <c r="K72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L72" s="6">
         <f>IF(COUNTA(D72:K72)=0,"",COUNTIF(D72:K72,"Sí")+0.5*COUNTIF(D72:K72,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M72" s="6" t="n"/>
-      <c r="N72" s="6" t="n"/>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 de la clase de seguridad, sin macro.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -15050,20 +16270,60 @@
           <t>Cloud-based machine learning for scalable classification of software requirements: Insights from the PROMISE dataset</t>
         </is>
       </c>
-      <c r="D77" s="7" t="n"/>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
-      <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
-      <c r="J77" s="7" t="n"/>
-      <c r="K77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L77" s="6">
         <f>IF(COUNTA(D77:K77)=0,"",COUNTIF(D77:K77,"Sí")+0.5*COUNTIF(D77:K77,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M77" s="6" t="n"/>
-      <c r="N77" s="6" t="n"/>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: SMOTE antes de la partición. QA4 parcial: F1 sin especificar el promedio.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -15709,20 +16969,60 @@
           <t>Large Language Model for Requirements Classification: An Ensemble Approach</t>
         </is>
       </c>
-      <c r="D94" s="7" t="n"/>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="7" t="n"/>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="7" t="n"/>
-      <c r="J94" s="7" t="n"/>
-      <c r="K94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L94" s="6">
         <f>IF(COUNTA(D94:K94)=0,"",COUNTIF(D94:K94,"Sí")+0.5*COUNTIF(D94:K94,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M94" s="6" t="n"/>
-      <c r="N94" s="6" t="n"/>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: partición no descrita. QA4 = 0: F1 global de una tarea binaria.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -16450,20 +17750,60 @@
           <t>An explainable method for security requirements classification through transformer models</t>
         </is>
       </c>
-      <c r="D117" s="7" t="n"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="n"/>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-      <c r="J117" s="7" t="n"/>
-      <c r="K117" s="7" t="n"/>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L117" s="6">
         <f>IF(COUNTA(D117:K117)=0,"",COUNTIF(D117:K117,"Sí")+0.5*COUNTIF(D117:K117,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M117" s="6" t="n"/>
-      <c r="N117" s="6" t="n"/>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N117" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 binario y matriz de confusión.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -16733,20 +18073,60 @@
           <t>Evaluating robustness of hierarchical and multi-label requirements classification: Effects of data partitioning and supervision design</t>
         </is>
       </c>
-      <c r="D126" s="7" t="n"/>
-      <c r="E126" s="7" t="n"/>
-      <c r="F126" s="7" t="n"/>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="7" t="n"/>
-      <c r="I126" s="7" t="n"/>
-      <c r="J126" s="7" t="n"/>
-      <c r="K126" s="7" t="n"/>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L126" s="6">
         <f>IF(COUNTA(D126:K126)=0,"",COUNTIF(D126:K126,"Sí")+0.5*COUNTIF(D126:K126,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M126" s="6" t="n"/>
-      <c r="N126" s="6" t="n"/>
+      <c r="M126" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N126" s="6" t="inlineStr">
+        <is>
+          <t>Cumple los ocho criterios.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
@@ -16975,20 +18355,60 @@
           <t>Hybrid approach for multilevel multi-class requirement classification: Impact of stop-word removal and data augmentation</t>
         </is>
       </c>
-      <c r="D132" s="7" t="n"/>
-      <c r="E132" s="7" t="n"/>
-      <c r="F132" s="7" t="n"/>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
-      <c r="J132" s="7" t="n"/>
-      <c r="K132" s="7" t="n"/>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L132" s="6">
         <f>IF(COUNTA(D132:K132)=0,"",COUNTIF(D132:K132,"Sí")+0.5*COUNTIF(D132:K132,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M132" s="6" t="n"/>
-      <c r="N132" s="6" t="n"/>
+      <c r="M132" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N132" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: aumentación previa a la partición. QA4 parcial: F1 sin promedio macro.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
@@ -17218,20 +18638,60 @@
           <t>RequiBERT: Transfer learning for software requirements classifications</t>
         </is>
       </c>
-      <c r="D141" s="7" t="n"/>
-      <c r="E141" s="7" t="n"/>
-      <c r="F141" s="7" t="n"/>
-      <c r="G141" s="7" t="n"/>
-      <c r="H141" s="7" t="n"/>
-      <c r="I141" s="7" t="n"/>
-      <c r="J141" s="7" t="n"/>
-      <c r="K141" s="7" t="n"/>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L141" s="6">
         <f>IF(COUNTA(D141:K141)=0,"",COUNTIF(D141:K141,"Sí")+0.5*COUNTIF(D141:K141,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M141" s="6" t="n"/>
-      <c r="N141" s="6" t="n"/>
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N141" s="6" t="inlineStr">
+        <is>
+          <t>QA4 completo: promedio de F1 por clase y valores por clase.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n">

--- a/RSL/formulario_extraccion_calidad.xlsx
+++ b/RSL/formulario_extraccion_calidad.xlsx
@@ -3194,31 +3194,123 @@
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="4" t="n"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n"/>
-      <c r="U28" s="4" t="n"/>
-      <c r="V28" s="4" t="n"/>
-      <c r="W28" s="4" t="n"/>
-      <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="4" t="n"/>
-      <c r="Z28" s="4" t="n"/>
-      <c r="AA28" s="4" t="n"/>
-      <c r="AB28" s="4" t="n"/>
-      <c r="AC28" s="4" t="n"/>
-      <c r="AD28" s="4" t="n"/>
-      <c r="AE28" s="4" t="n"/>
-      <c r="AF28" s="4" t="n"/>
-      <c r="AG28" s="4" t="n"/>
-      <c r="AH28" s="4" t="n"/>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (625)</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>Ocho clasificadores DL con cinco embeddings (TF-IDF, CBOW, Skip-gram, GloVe, Word2Vec); PCA y prueba de suma de rangos</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>SMOTE sobre el conjunto y después validación cruzada de 5 pliegues</t>
+        </is>
+      </c>
+      <c r="X28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y28" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, F-measure y AUC</t>
+        </is>
+      </c>
+      <c r="Z28" s="4" t="inlineStr"/>
+      <c r="AA28" s="4" t="inlineStr">
+        <is>
+          <t>Comparación por diagramas de caja; TF-IDF el mejor embedding</t>
+        </is>
+      </c>
+      <c r="AB28" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Combinaciones con y sin SMOTE y selección de rasgos</t>
+        </is>
+      </c>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF28" s="4" t="inlineStr">
+        <is>
+          <t>No se identificó una sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG28" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
+          <t>Prueba de Friedman. El orden descrito (balancear con SMOTE y luego partir en 5 pliegues) permite que muestras sintéticas derivadas de requerimientos de prueba queden en entrenamiento.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -3318,31 +3410,123 @@
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="4" t="n"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
-      <c r="U30" s="4" t="n"/>
-      <c r="V30" s="4" t="n"/>
-      <c r="W30" s="4" t="n"/>
-      <c r="X30" s="4" t="n"/>
-      <c r="Y30" s="4" t="n"/>
-      <c r="Z30" s="4" t="n"/>
-      <c r="AA30" s="4" t="n"/>
-      <c r="AB30" s="4" t="n"/>
-      <c r="AC30" s="4" t="n"/>
-      <c r="AD30" s="4" t="n"/>
-      <c r="AE30" s="4" t="n"/>
-      <c r="AF30" s="4" t="n"/>
-      <c r="AG30" s="4" t="n"/>
-      <c r="AH30" s="4" t="n"/>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas en árabe de apps de reparto (Google Play), dos versiones del conjunto (≈8000 reseñas)</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Árabe</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>≈8000</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>5 (usabilidad, fiabilidad, desempeño, comportamiento, seguridad) y 4</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>Aumentación con EDA (TextAttack EasyDataAugmenter, intercambio de palabras)</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>Híbrido RNN + 2 LSTM; ML clásico (RF, SVC, KNN, NB, DT) y DL (ANN, LSTM, BiLSTM)</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>No se precisa la partición en el texto revisado</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y30" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, exactitud y F1</t>
+        </is>
+      </c>
+      <c r="Z30" s="4" t="inlineStr"/>
+      <c r="AA30" s="4" t="inlineStr">
+        <is>
+          <t>Híbrido 0.96; RF y SVC 0.94 con aumentación; sin aumentación, los peores 0.38</t>
+        </is>
+      </c>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>Matrices de confusión con y sin aumentación</t>
+        </is>
+      </c>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>ML y DL con y sin aumentación</t>
+        </is>
+      </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF30" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AG30" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
+          <t>Uno de los pocos estudios que usan EDA; compara con y sin aumentación, pero no contra otras técnicas. Texto en árabe.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -3538,8 +3722,16 @@
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>CE2</t>
+        </is>
+      </c>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
@@ -3562,7 +3754,11 @@
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="4" t="n"/>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>Vincula issues de Chrome y Moodle con 71 requerimientos de privacidad de una taxonomía (alineación y trazabilidad, evaluada con MRR y Recall@k); las clases no son tipos de requerimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -3654,31 +3850,123 @@
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="4" t="n"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
-      <c r="U34" s="4" t="n"/>
-      <c r="V34" s="4" t="n"/>
-      <c r="W34" s="4" t="n"/>
-      <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n"/>
-      <c r="Z34" s="4" t="n"/>
-      <c r="AA34" s="4" t="n"/>
-      <c r="AB34" s="4" t="n"/>
-      <c r="AC34" s="4" t="n"/>
-      <c r="AD34" s="4" t="n"/>
-      <c r="AE34" s="4" t="n"/>
-      <c r="AF34" s="4" t="n"/>
-      <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="4" t="n"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto turco de 4600 requerimientos de proyectos reales</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Turco</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>2 (parcialmente desbalanceadas)</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>20 algoritmos: ML clásico, DL (CNN, LSTM, GRU) y transformers (BERTurk y otros)</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada (detalles por grupo de algoritmos)</t>
+        </is>
+      </c>
+      <c r="X34" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y34" s="4" t="inlineStr">
+        <is>
+          <t>F-score y métricas relacionadas</t>
+        </is>
+      </c>
+      <c r="Z34" s="4" t="inlineStr"/>
+      <c r="AA34" s="4" t="inlineStr">
+        <is>
+          <t>BERTurk 0.95</t>
+        </is>
+      </c>
+      <c r="AB34" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>20 algoritmos</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE34" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="AF34" s="4" t="inlineStr">
+        <is>
+          <t>Limitaciones del conjunto</t>
+        </is>
+      </c>
+      <c r="AG34" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
+          <t>Primer conjunto en turco; muestra que los transformers dominan también fuera del inglés.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -3990,31 +4278,123 @@
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="4" t="n"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-      <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n"/>
-      <c r="U38" s="4" t="n"/>
-      <c r="V38" s="4" t="n"/>
-      <c r="W38" s="4" t="n"/>
-      <c r="X38" s="4" t="n"/>
-      <c r="Y38" s="4" t="n"/>
-      <c r="Z38" s="4" t="n"/>
-      <c r="AA38" s="4" t="n"/>
-      <c r="AB38" s="4" t="n"/>
-      <c r="AC38" s="4" t="n"/>
-      <c r="AD38" s="4" t="n"/>
-      <c r="AE38" s="4" t="n"/>
-      <c r="AF38" s="4" t="n"/>
-      <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="4" t="n"/>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR con muestras añadidas manualmente</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>625 más muestras añadidas</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>Muestras añadidas manualmente a las clases minoritarias</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>XLNet, BERT, DistilBERT, DistilRoBERTa, ELECTRA</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>Partición 80/20</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y38" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, F1 y MCC</t>
+        </is>
+      </c>
+      <c r="Z38" s="4" t="inlineStr"/>
+      <c r="AA38" s="4" t="inlineStr">
+        <is>
+          <t>XLNet 0.915 (exactitud, precisión, exhaustividad y F1 iguales); MCC 0.907</t>
+        </is>
+      </c>
+      <c r="AB38" s="4" t="inlineStr">
+        <is>
+          <t>Matriz de confusión de 12 clases</t>
+        </is>
+      </c>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Otros transformers y estudios previos</t>
+        </is>
+      </c>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF38" s="4" t="inlineStr">
+        <is>
+          <t>Sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG38" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2</t>
+        </is>
+      </c>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
+          <t>Que exactitud, precisión, exhaustividad y F1 coincidan indica promedios micro. No precisa si las muestras añadidas a mano quedaron solo en entrenamiento.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4338,8 +4718,16 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>CE1</t>
+        </is>
+      </c>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
@@ -4362,7 +4750,11 @@
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="4" t="n"/>
+      <c r="AH42" s="4" t="inlineStr">
+        <is>
+          <t>Clasifica requerimientos de sistemas aeroespaciales (regulaciones de certificación) en diseño, funcional y desempeño; no son requerimientos de software.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4398,31 +4790,123 @@
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="4" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-      <c r="R43" s="4" t="n"/>
-      <c r="S43" s="4" t="n"/>
-      <c r="T43" s="4" t="n"/>
-      <c r="U43" s="4" t="n"/>
-      <c r="V43" s="4" t="n"/>
-      <c r="W43" s="4" t="n"/>
-      <c r="X43" s="4" t="n"/>
-      <c r="Y43" s="4" t="n"/>
-      <c r="Z43" s="4" t="n"/>
-      <c r="AA43" s="4" t="n"/>
-      <c r="AB43" s="4" t="n"/>
-      <c r="AC43" s="4" t="n"/>
-      <c r="AD43" s="4" t="n"/>
-      <c r="AE43" s="4" t="n"/>
-      <c r="AF43" s="4" t="n"/>
-      <c r="AG43" s="4" t="n"/>
-      <c r="AH43" s="4" t="n"/>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>1135 requerimientos de seguridad unificados de varios conjuntos (DOSSPRE, Riaz, CCHIT y otros)</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>3 (confidencialidad, integridad, disponibilidad)</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (descarta la aumentación)</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>SVM, KNN, RF, GB y BNB con TF-IDF o sentence-transformer</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>Partición 70/30 y validación cruzada de 10 pliegues</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y43" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z43" s="4" t="inlineStr"/>
+      <c r="AA43" s="4" t="inlineStr">
+        <is>
+          <t>SVM con sentence-transformer: exactitud 0.87</t>
+        </is>
+      </c>
+      <c r="AB43" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta por clase</t>
+        </is>
+      </c>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>TF-IDF frente a sentence-transformer</t>
+        </is>
+      </c>
+      <c r="AD43" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE43" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF43" s="4" t="inlineStr">
+        <is>
+          <t>Anotación sin otros expertos</t>
+        </is>
+      </c>
+      <c r="AG43" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR4</t>
+        </is>
+      </c>
+      <c r="AH43" s="4" t="inlineStr">
+        <is>
+          <t>Subclasifica requerimientos de seguridad según la tríada CIA.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -4586,31 +5070,123 @@
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="4" t="n"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
-      <c r="O46" s="4" t="n"/>
-      <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="4" t="n"/>
-      <c r="R46" s="4" t="n"/>
-      <c r="S46" s="4" t="n"/>
-      <c r="T46" s="4" t="n"/>
-      <c r="U46" s="4" t="n"/>
-      <c r="V46" s="4" t="n"/>
-      <c r="W46" s="4" t="n"/>
-      <c r="X46" s="4" t="n"/>
-      <c r="Y46" s="4" t="n"/>
-      <c r="Z46" s="4" t="n"/>
-      <c r="AA46" s="4" t="n"/>
-      <c r="AB46" s="4" t="n"/>
-      <c r="AC46" s="4" t="n"/>
-      <c r="AD46" s="4" t="n"/>
-      <c r="AE46" s="4" t="n"/>
-      <c r="AF46" s="4" t="n"/>
-      <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="4" t="n"/>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE_exp (969, 12 tipos) y conjuntos nuevos sin etiquetar</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>2 (con 12 tipos en el conjunto original)</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>SMOTE-Tomek sobre los embeddings</t>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>EnsCL-CatBoost: ensamble de Doc2Vec, Word2Vec y FastText con aprendizaje contrastivo y CatBoost; cinco clasificadores ML</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>SMOTE-Tomek sobre todo el conjunto y después partición 80/20 y validación cruzada de 10 pliegues</t>
+        </is>
+      </c>
+      <c r="X46" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y46" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z46" s="4" t="inlineStr"/>
+      <c r="AA46" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud 0.94</t>
+        </is>
+      </c>
+      <c r="AB46" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Cinco clasificadores ML con embeddings tradicionales</t>
+        </is>
+      </c>
+      <c r="AD46" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE46" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF46" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG46" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH46" s="4" t="inlineStr">
+        <is>
+          <t>El pseudocódigo aplica train_test_split a las variables ya remuestreadas (featuresres, labelsres): SMOTE-Tomek antes de partir, con riesgo de fuga. Elimina duplicados exactos antes. Es el único estudio con SMOTE-Tomek del corpus leído.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5370,8 +5946,16 @@
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>CE1</t>
+        </is>
+      </c>
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
@@ -5394,7 +5978,11 @@
       <c r="AE54" s="4" t="n"/>
       <c r="AF54" s="4" t="n"/>
       <c r="AG54" s="4" t="n"/>
-      <c r="AH54" s="4" t="n"/>
+      <c r="AH54" s="4" t="inlineStr">
+        <is>
+          <t>Clasifica requerimientos de misiones espaciales (objetivos científicos, desempeño, carga útil, ingeniería) para MBSE; no son requerimientos de software.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -6170,31 +6758,123 @@
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="4" t="n"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
-      <c r="O64" s="4" t="n"/>
-      <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n"/>
-      <c r="R64" s="4" t="n"/>
-      <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n"/>
-      <c r="U64" s="4" t="n"/>
-      <c r="V64" s="4" t="n"/>
-      <c r="W64" s="4" t="n"/>
-      <c r="X64" s="4" t="n"/>
-      <c r="Y64" s="4" t="n"/>
-      <c r="Z64" s="4" t="n"/>
-      <c r="AA64" s="4" t="n"/>
-      <c r="AB64" s="4" t="n"/>
-      <c r="AC64" s="4" t="n"/>
-      <c r="AD64" s="4" t="n"/>
-      <c r="AE64" s="4" t="n"/>
-      <c r="AF64" s="4" t="n"/>
-      <c r="AG64" s="4" t="n"/>
-      <c r="AH64" s="4" t="n"/>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>Historias de usuario</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>10 006 historias de usuario únicas etiquetadas por los autores (101 duplicados eliminados)</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>10 006</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>8 (siete características ISO/IEC 25010 y FR)</t>
+        </is>
+      </c>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>Focal Loss</t>
+        </is>
+      </c>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U64" s="4" t="inlineStr">
+        <is>
+          <t>BERT, RoBERTa, XLNet y DistilBERT con optimización bayesiana de hiperparámetros</t>
+        </is>
+      </c>
+      <c r="V64" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W64" s="4" t="inlineStr">
+        <is>
+          <t>Partición aleatoria 80/20 en subconjuntos disjuntos, tras quitar duplicados</t>
+        </is>
+      </c>
+      <c r="X64" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y64" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z64" s="4" t="inlineStr"/>
+      <c r="AA64" s="4" t="inlineStr">
+        <is>
+          <t>BERT 0.934</t>
+        </is>
+      </c>
+      <c r="AB64" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta por clase en el texto revisado</t>
+        </is>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Enfoques basados en reglas y ML clásico de la literatura</t>
+        </is>
+      </c>
+      <c r="AD64" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE64" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF64" s="4" t="inlineStr">
+        <is>
+          <t>Sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG64" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH64" s="4" t="inlineStr">
+        <is>
+          <t>Semilla del estado del arte. El conjunto de historias de usuario se publica en GitHub (a-re22/Agile_Req_NFRs). Usa Focal Loss en lugar de remuestreo.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -6486,31 +7166,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n"/>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
-      <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
-      <c r="P69" s="4" t="n"/>
-      <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="4" t="n"/>
-      <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
-      <c r="U69" s="4" t="n"/>
-      <c r="V69" s="4" t="n"/>
-      <c r="W69" s="4" t="n"/>
-      <c r="X69" s="4" t="n"/>
-      <c r="Y69" s="4" t="n"/>
-      <c r="Z69" s="4" t="n"/>
-      <c r="AA69" s="4" t="n"/>
-      <c r="AB69" s="4" t="n"/>
-      <c r="AC69" s="4" t="n"/>
-      <c r="AD69" s="4" t="n"/>
-      <c r="AE69" s="4" t="n"/>
-      <c r="AF69" s="4" t="n"/>
-      <c r="AG69" s="4" t="n"/>
-      <c r="AH69" s="4" t="n"/>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE y FR_NFR</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>625 y FR_NFR</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Binaria FR/NFR</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U69" s="4" t="inlineStr">
+        <is>
+          <t>BERT con análisis de hiperparámetros y del tamaño del conjunto</t>
+        </is>
+      </c>
+      <c r="V69" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W69" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 10 pliegues</t>
+        </is>
+      </c>
+      <c r="X69" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y69" s="4" t="inlineStr">
+        <is>
+          <t>F1 por clase (FR y NFR) y promedio</t>
+        </is>
+      </c>
+      <c r="Z69" s="4" t="inlineStr"/>
+      <c r="AA69" s="4" t="inlineStr">
+        <is>
+          <t>0.99 en PROMISE y 0.97 en FR_NFR</t>
+        </is>
+      </c>
+      <c r="AB69" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Estudios previos en PROMISE</t>
+        </is>
+      </c>
+      <c r="AD69" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE69" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF69" s="4" t="inlineStr">
+        <is>
+          <t>Sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG69" s="4" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="AH69" s="4" t="inlineStr">
+        <is>
+          <t>Código en GitHub (omercomail/Requirements-BERT). F1 de 0.99 en PROMISE sin control de duplicados.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -7502,31 +8274,123 @@
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="4" t="n"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K79" s="4" t="n"/>
-      <c r="L79" s="4" t="n"/>
-      <c r="M79" s="4" t="n"/>
-      <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
-      <c r="P79" s="4" t="n"/>
-      <c r="Q79" s="4" t="n"/>
-      <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="n"/>
-      <c r="T79" s="4" t="n"/>
-      <c r="U79" s="4" t="n"/>
-      <c r="V79" s="4" t="n"/>
-      <c r="W79" s="4" t="n"/>
-      <c r="X79" s="4" t="n"/>
-      <c r="Y79" s="4" t="n"/>
-      <c r="Z79" s="4" t="n"/>
-      <c r="AA79" s="4" t="n"/>
-      <c r="AB79" s="4" t="n"/>
-      <c r="AC79" s="4" t="n"/>
-      <c r="AD79" s="4" t="n"/>
-      <c r="AE79" s="4" t="n"/>
-      <c r="AF79" s="4" t="n"/>
-      <c r="AG79" s="4" t="n"/>
-      <c r="AH79" s="4" t="n"/>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>803 NFR derivados de PROMISE y PROMISE_exp (367 de seguridad, 427 de no seguridad)</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>Binaria seguridad/no seguridad; 7 categorías de seguridad</t>
+        </is>
+      </c>
+      <c r="R79" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S79" s="4" t="inlineStr">
+        <is>
+          <t>Paráfrasis con T5-small</t>
+        </is>
+      </c>
+      <c r="T79" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="U79" s="4" t="inlineStr">
+        <is>
+          <t>BERT, DistilBERT, ANN, LSTM, CNN; LR, SVM y XGBoost para la multiclase</t>
+        </is>
+      </c>
+      <c r="V79" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W79" s="4" t="inlineStr">
+        <is>
+          <t>Evaluación en un conjunto de validación (partición no precisada)</t>
+        </is>
+      </c>
+      <c r="X79" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y79" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, F1 y ROC-AUC</t>
+        </is>
+      </c>
+      <c r="Z79" s="4" t="inlineStr"/>
+      <c r="AA79" s="4" t="inlineStr">
+        <is>
+          <t>BERT supera a ANN, LSTM y CNN; detalle por épocas</t>
+        </is>
+      </c>
+      <c r="AB79" s="4" t="inlineStr">
+        <is>
+          <t>Por categoría en la multiclase</t>
+        </is>
+      </c>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>ANN, LSTM, CNN</t>
+        </is>
+      </c>
+      <c r="AD79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF79" s="4" t="inlineStr">
+        <is>
+          <t>Tamaño y desbalance del conjunto</t>
+        </is>
+      </c>
+      <c r="AG79" s="4" t="inlineStr">
+        <is>
+          <t>PR2</t>
+        </is>
+      </c>
+      <c r="AH79" s="4" t="inlineStr">
+        <is>
+          <t>Los resultados se reportan sobre el conjunto de validación, no sobre una prueba separada.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -7694,31 +8558,123 @@
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="4" t="n"/>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="4" t="n"/>
-      <c r="O82" s="4" t="n"/>
-      <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="n"/>
-      <c r="R82" s="4" t="n"/>
-      <c r="S82" s="4" t="n"/>
-      <c r="T82" s="4" t="n"/>
-      <c r="U82" s="4" t="n"/>
-      <c r="V82" s="4" t="n"/>
-      <c r="W82" s="4" t="n"/>
-      <c r="X82" s="4" t="n"/>
-      <c r="Y82" s="4" t="n"/>
-      <c r="Z82" s="4" t="n"/>
-      <c r="AA82" s="4" t="n"/>
-      <c r="AB82" s="4" t="n"/>
-      <c r="AC82" s="4" t="n"/>
-      <c r="AD82" s="4" t="n"/>
-      <c r="AE82" s="4" t="n"/>
-      <c r="AF82" s="4" t="n"/>
-      <c r="AG82" s="4" t="n"/>
-      <c r="AH82" s="4" t="n"/>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>SecReq (497: 166 seguridad, 331 no seguridad) y tres versiones aumentadas</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>2 (seguridad / no seguridad)</t>
+        </is>
+      </c>
+      <c r="R82" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S82" s="4" t="inlineStr">
+        <is>
+          <t>Tres aumentaciones comparadas: embeddings contextuales, retrotraducción y paráfrasis; además SetFit (few-shot)</t>
+        </is>
+      </c>
+      <c r="T82" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U82" s="4" t="inlineStr">
+        <is>
+          <t>BERT, DistilBERT, RoBERTa y XLNet; SetFit</t>
+        </is>
+      </c>
+      <c r="V82" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W82" s="4" t="inlineStr">
+        <is>
+          <t>Partición 80/10/10; aumentación sobre el conjunto de entrenamiento; mismos hiperparámetros para las cuatro versiones</t>
+        </is>
+      </c>
+      <c r="X82" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y82" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, precisión, exhaustividad, F1 y matriz de confusión</t>
+        </is>
+      </c>
+      <c r="Z82" s="4" t="inlineStr"/>
+      <c r="AA82" s="4" t="inlineStr">
+        <is>
+          <t>Sin aumentación, exactitud 0.89–0.90; BERT con embeddings contextuales 0.94; RoBERTa sensible a la aumentación</t>
+        </is>
+      </c>
+      <c r="AB82" s="4" t="inlineStr">
+        <is>
+          <t>Matrices de confusión con y sin aumentación</t>
+        </is>
+      </c>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto original sin aumentar</t>
+        </is>
+      </c>
+      <c r="AD82" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE82" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF82" s="4" t="inlineStr">
+        <is>
+          <t>Sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG82" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH82" s="4" t="inlineStr">
+        <is>
+          <t>Único estudio leído que compara varias técnicas de aumentación con los mismos transformers y la misma partición, en la tarea binaria de seguridad. El efecto depende del modelo: la paráfrasis y la retrotraducción no ayudan a todos.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -8406,31 +9362,123 @@
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="4" t="n"/>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="4" t="n"/>
-      <c r="N89" s="4" t="n"/>
-      <c r="O89" s="4" t="n"/>
-      <c r="P89" s="4" t="n"/>
-      <c r="Q89" s="4" t="n"/>
-      <c r="R89" s="4" t="n"/>
-      <c r="S89" s="4" t="n"/>
-      <c r="T89" s="4" t="n"/>
-      <c r="U89" s="4" t="n"/>
-      <c r="V89" s="4" t="n"/>
-      <c r="W89" s="4" t="n"/>
-      <c r="X89" s="4" t="n"/>
-      <c r="Y89" s="4" t="n"/>
-      <c r="Z89" s="4" t="n"/>
-      <c r="AA89" s="4" t="n"/>
-      <c r="AB89" s="4" t="n"/>
-      <c r="AC89" s="4" t="n"/>
-      <c r="AD89" s="4" t="n"/>
-      <c r="AE89" s="4" t="n"/>
-      <c r="AF89" s="4" t="n"/>
-      <c r="AG89" s="4" t="n"/>
-      <c r="AH89" s="4" t="n"/>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625: 255 FR, 370 NFR)</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="P89" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR y subclases de NFR</t>
+        </is>
+      </c>
+      <c r="R89" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S89" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T89" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U89" s="4" t="inlineStr">
+        <is>
+          <t>GPT-4o y LLaMA 3.3 70B en zero-shot con cuatro temperaturas</t>
+        </is>
+      </c>
+      <c r="V89" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador zero-shot</t>
+        </is>
+      </c>
+      <c r="W89" s="4" t="inlineStr">
+        <is>
+          <t>Clasificación por lotes de 100 requerimientos; tres ejecuciones por temperatura</t>
+        </is>
+      </c>
+      <c r="X89" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="Y89" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad, F1 y acuerdo con las etiquetas humanas</t>
+        </is>
+      </c>
+      <c r="Z89" s="4" t="inlineStr"/>
+      <c r="AA89" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR: F1 medio 0.76–0.85 según modelo y temperatura</t>
+        </is>
+      </c>
+      <c r="AB89" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta por clase</t>
+        </is>
+      </c>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Etiquetas humanas de PROMISE</t>
+        </is>
+      </c>
+      <c r="AD89" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE89" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF89" s="4" t="inlineStr">
+        <is>
+          <t>Riesgo de clasificación errónea con LLM</t>
+        </is>
+      </c>
+      <c r="AG89" s="4" t="inlineStr">
+        <is>
+          <t>PR3</t>
+        </is>
+      </c>
+      <c r="AH89" s="4" t="inlineStr">
+        <is>
+          <t>LLaMA 3.3 es más consistente entre ejecuciones que GPT-4o. La temperatura cambia el equilibrio entre precisión y exhaustividad.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -9526,31 +10574,123 @@
           <t>PROMISE; SecReq</t>
         </is>
       </c>
-      <c r="J101" s="4" t="n"/>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K101" s="4" t="n"/>
-      <c r="L101" s="4" t="n"/>
-      <c r="M101" s="4" t="n"/>
-      <c r="N101" s="4" t="n"/>
-      <c r="O101" s="4" t="n"/>
-      <c r="P101" s="4" t="n"/>
-      <c r="Q101" s="4" t="n"/>
-      <c r="R101" s="4" t="n"/>
-      <c r="S101" s="4" t="n"/>
-      <c r="T101" s="4" t="n"/>
-      <c r="U101" s="4" t="n"/>
-      <c r="V101" s="4" t="n"/>
-      <c r="W101" s="4" t="n"/>
-      <c r="X101" s="4" t="n"/>
-      <c r="Y101" s="4" t="n"/>
-      <c r="Z101" s="4" t="n"/>
-      <c r="AA101" s="4" t="n"/>
-      <c r="AB101" s="4" t="n"/>
-      <c r="AC101" s="4" t="n"/>
-      <c r="AD101" s="4" t="n"/>
-      <c r="AE101" s="4" t="n"/>
-      <c r="AF101" s="4" t="n"/>
-      <c r="AG101" s="4" t="n"/>
-      <c r="AH101" s="4" t="n"/>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE y SecReq</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>625 y SecReq</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="inlineStr">
+        <is>
+          <t>Cinco tareas: FR/NFR, 4 NFR frecuentes, seguridad y otras</t>
+        </is>
+      </c>
+      <c r="R101" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S101" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna; restringe la multiclase a las 4 NFR frecuentes por el desbalance</t>
+        </is>
+      </c>
+      <c r="T101" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U101" s="4" t="inlineStr">
+        <is>
+          <t>BART-mnli y RoBERTa-mnli (zero-shot); All-MPNET y All-DistilRoBERTa (few-shot); GPT-4o y Llama 3 (zero- y few-shot)</t>
+        </is>
+      </c>
+      <c r="V101" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador few-shot</t>
+        </is>
+      </c>
+      <c r="W101" s="4" t="inlineStr">
+        <is>
+          <t>Los ejemplos del prompt se excluyen del conjunto de prueba; comparación con un modelo supervisado 80/20</t>
+        </is>
+      </c>
+      <c r="X101" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y101" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 por clase; promedios macro</t>
+        </is>
+      </c>
+      <c r="Z101" s="4" t="inlineStr">
+        <is>
+          <t>NFR multiclase: GPT-4o few-shot 0.796, GPT-4o 0.78, Llama 3 0.77; SBERT 0.655</t>
+        </is>
+      </c>
+      <c r="AA101" s="4" t="inlineStr"/>
+      <c r="AB101" s="4" t="inlineStr">
+        <is>
+          <t>Por clase en tablas</t>
+        </is>
+      </c>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>NoRBERT, SBERT y modelos supervisados</t>
+        </is>
+      </c>
+      <c r="AD101" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE101" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF101" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG101" s="4" t="inlineStr">
+        <is>
+          <t>PR3, PR5</t>
+        </is>
+      </c>
+      <c r="AH101" s="4" t="inlineStr">
+        <is>
+          <t>Prueba de McNemar. NoRBERT sigue siendo superior en FR/NFR. Excluye los ejemplos few-shot de la prueba para evitar fuga. Paquete en figshare.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -10462,31 +11602,123 @@
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="4" t="n"/>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K113" s="4" t="n"/>
-      <c r="L113" s="4" t="n"/>
-      <c r="M113" s="4" t="n"/>
-      <c r="N113" s="4" t="n"/>
-      <c r="O113" s="4" t="n"/>
-      <c r="P113" s="4" t="n"/>
-      <c r="Q113" s="4" t="n"/>
-      <c r="R113" s="4" t="n"/>
-      <c r="S113" s="4" t="n"/>
-      <c r="T113" s="4" t="n"/>
-      <c r="U113" s="4" t="n"/>
-      <c r="V113" s="4" t="n"/>
-      <c r="W113" s="4" t="n"/>
-      <c r="X113" s="4" t="n"/>
-      <c r="Y113" s="4" t="n"/>
-      <c r="Z113" s="4" t="n"/>
-      <c r="AA113" s="4" t="n"/>
-      <c r="AB113" s="4" t="n"/>
-      <c r="AC113" s="4" t="n"/>
-      <c r="AD113" s="4" t="n"/>
-      <c r="AE113" s="4" t="n"/>
-      <c r="AF113" s="4" t="n"/>
-      <c r="AG113" s="4" t="n"/>
-      <c r="AH113" s="4" t="n"/>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M113" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE NFR más 50 requerimientos clínicos</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="P113" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="inlineStr">
+        <is>
+          <t>5 (seguridad, fiabilidad, usabilidad, desempeño, explicabilidad)</t>
+        </is>
+      </c>
+      <c r="R113" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S113" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T113" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U113" s="4" t="inlineStr">
+        <is>
+          <t>BERT frente a SVM dentro de un marco con ontologías para salud</t>
+        </is>
+      </c>
+      <c r="V113" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W113" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada 80/20 con validación cruzada de 5 pliegues en el entrenamiento</t>
+        </is>
+      </c>
+      <c r="X113" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y113" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1</t>
+        </is>
+      </c>
+      <c r="Z113" s="4" t="inlineStr"/>
+      <c r="AA113" s="4" t="inlineStr">
+        <is>
+          <t>BERT 0.87–0.88</t>
+        </is>
+      </c>
+      <c r="AB113" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>SVM con TF-IDF</t>
+        </is>
+      </c>
+      <c r="AD113" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE113" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF113" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG113" s="4" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="AH113" s="4" t="inlineStr">
+        <is>
+          <t>La clasificación es un módulo de un marco más amplio. Prueba t pareada por categoría.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
@@ -10530,31 +11762,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J114" s="4" t="n"/>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K114" s="4" t="n"/>
-      <c r="L114" s="4" t="n"/>
-      <c r="M114" s="4" t="n"/>
-      <c r="N114" s="4" t="n"/>
-      <c r="O114" s="4" t="n"/>
-      <c r="P114" s="4" t="n"/>
-      <c r="Q114" s="4" t="n"/>
-      <c r="R114" s="4" t="n"/>
-      <c r="S114" s="4" t="n"/>
-      <c r="T114" s="4" t="n"/>
-      <c r="U114" s="4" t="n"/>
-      <c r="V114" s="4" t="n"/>
-      <c r="W114" s="4" t="n"/>
-      <c r="X114" s="4" t="n"/>
-      <c r="Y114" s="4" t="n"/>
-      <c r="Z114" s="4" t="n"/>
-      <c r="AA114" s="4" t="n"/>
-      <c r="AB114" s="4" t="n"/>
-      <c r="AC114" s="4" t="n"/>
-      <c r="AD114" s="4" t="n"/>
-      <c r="AE114" s="4" t="n"/>
-      <c r="AF114" s="4" t="n"/>
-      <c r="AG114" s="4" t="n"/>
-      <c r="AH114" s="4" t="n"/>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (binaria, 4 y 10 clases; multietiqueta) y EHR</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>625 y EHR</t>
+        </is>
+      </c>
+      <c r="P114" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="inlineStr">
+        <is>
+          <t>Binaria, 4, 10 y multietiqueta</t>
+        </is>
+      </c>
+      <c r="R114" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S114" s="4" t="inlineStr">
+        <is>
+          <t>Aumentación adaptativa ponderada por clase y longitud: diccionarios de dominio y modelos transformer, frente a aumentación tradicional</t>
+        </is>
+      </c>
+      <c r="T114" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U114" s="4" t="inlineStr">
+        <is>
+          <t>BiGRU</t>
+        </is>
+      </c>
+      <c r="V114" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W114" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada estratificada de 5 pliegues; aumentación sobre el subconjunto de entrenamiento</t>
+        </is>
+      </c>
+      <c r="X114" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y114" s="4" t="inlineStr">
+        <is>
+          <t>F1 macro, precisión y exhaustividad</t>
+        </is>
+      </c>
+      <c r="Z114" s="4" t="inlineStr">
+        <is>
+          <t>+6.7 puntos en PROMISE de 10 clases; multietiqueta 0.841 frente a 0.775 sin aumentación</t>
+        </is>
+      </c>
+      <c r="AA114" s="4" t="inlineStr"/>
+      <c r="AB114" s="4" t="inlineStr">
+        <is>
+          <t>Hasta +9.3 puntos en las clases infrarrepresentadas</t>
+        </is>
+      </c>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Sin aumentación y aumentación uniforme tradicional</t>
+        </is>
+      </c>
+      <c r="AD114" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE114" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="AF114" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AG114" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH114" s="4" t="inlineStr">
+        <is>
+          <t>Compara varias estrategias de aumentación en la tarea multiclase de PROMISE, pero con un BiGRU, no con BERT, y sin incluir TAOS ni SMOTE-Tomek. Está entre las semillas alternativas.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -10658,31 +11982,127 @@
           <t>PROMISE; PROMISE_exp</t>
         </is>
       </c>
-      <c r="J116" s="4" t="n"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K116" s="4" t="n"/>
-      <c r="L116" s="4" t="n"/>
-      <c r="M116" s="4" t="n"/>
-      <c r="N116" s="4" t="n"/>
-      <c r="O116" s="4" t="n"/>
-      <c r="P116" s="4" t="n"/>
-      <c r="Q116" s="4" t="n"/>
-      <c r="R116" s="4" t="n"/>
-      <c r="S116" s="4" t="n"/>
-      <c r="T116" s="4" t="n"/>
-      <c r="U116" s="4" t="n"/>
-      <c r="V116" s="4" t="n"/>
-      <c r="W116" s="4" t="n"/>
-      <c r="X116" s="4" t="n"/>
-      <c r="Y116" s="4" t="n"/>
-      <c r="Z116" s="4" t="n"/>
-      <c r="AA116" s="4" t="n"/>
-      <c r="AB116" s="4" t="n"/>
-      <c r="AC116" s="4" t="n"/>
-      <c r="AD116" s="4" t="n"/>
-      <c r="AE116" s="4" t="n"/>
-      <c r="AF116" s="4" t="n"/>
-      <c r="AG116" s="4" t="n"/>
-      <c r="AH116" s="4" t="n"/>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M116" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE y PROMISE_exp</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>625 y 969</t>
+        </is>
+      </c>
+      <c r="P116" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase FR+NFR</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R116" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S116" s="4" t="inlineStr">
+        <is>
+          <t>Aumentación dirigida que preserva la semántica en las clases minoritarias</t>
+        </is>
+      </c>
+      <c r="T116" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U116" s="4" t="inlineStr">
+        <is>
+          <t>Fusión de rasgos BERT + RoBERTa; BERT y RoBERTa solos</t>
+        </is>
+      </c>
+      <c r="V116" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W116" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada 70/15/15 antes de aumentar</t>
+        </is>
+      </c>
+      <c r="X116" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y116" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, F1 macro y ponderado, F1 por clase</t>
+        </is>
+      </c>
+      <c r="Z116" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE 0.84; PROMISE_exp 0.90</t>
+        </is>
+      </c>
+      <c r="AA116" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE 0.91; PROMISE_exp 0.93</t>
+        </is>
+      </c>
+      <c r="AB116" s="4" t="inlineStr">
+        <is>
+          <t>Mejora en las NFR minoritarias; alta varianza en las raras</t>
+        </is>
+      </c>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>BERT, RoBERTa y estado del arte</t>
+        </is>
+      </c>
+      <c r="AD116" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE116" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF116" s="4" t="inlineStr">
+        <is>
+          <t>Sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG116" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR2, PR5</t>
+        </is>
+      </c>
+      <c r="AH116" s="4" t="inlineStr">
+        <is>
+          <t>Parte el conjunto antes de aumentar 'para prevenir la fuga'. Prueba exacta de McNemar e intervalos de confianza. Código en GitHub.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -11130,31 +12550,127 @@
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr"/>
-      <c r="J122" s="4" t="n"/>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="n"/>
-      <c r="L122" s="4" t="n"/>
-      <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="n"/>
-      <c r="O122" s="4" t="n"/>
-      <c r="P122" s="4" t="n"/>
-      <c r="Q122" s="4" t="n"/>
-      <c r="R122" s="4" t="n"/>
-      <c r="S122" s="4" t="n"/>
-      <c r="T122" s="4" t="n"/>
-      <c r="U122" s="4" t="n"/>
-      <c r="V122" s="4" t="n"/>
-      <c r="W122" s="4" t="n"/>
-      <c r="X122" s="4" t="n"/>
-      <c r="Y122" s="4" t="n"/>
-      <c r="Z122" s="4" t="n"/>
-      <c r="AA122" s="4" t="n"/>
-      <c r="AB122" s="4" t="n"/>
-      <c r="AC122" s="4" t="n"/>
-      <c r="AD122" s="4" t="n"/>
-      <c r="AE122" s="4" t="n"/>
-      <c r="AF122" s="4" t="n"/>
-      <c r="AG122" s="4" t="n"/>
-      <c r="AH122" s="4" t="n"/>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>Corpus FR–NFR Re-Distill derivado de PROMISE y PURE</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>No se precisa en el texto revisado</t>
+        </is>
+      </c>
+      <c r="P122" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R122" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S122" s="4" t="inlineStr">
+        <is>
+          <t>Focal Loss</t>
+        </is>
+      </c>
+      <c r="T122" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U122" s="4" t="inlineStr">
+        <is>
+          <t>Codificador de dominio Re-Distill con contexto del FR asociado; BERT, RoBERTa y MPNet</t>
+        </is>
+      </c>
+      <c r="V122" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W122" s="4" t="inlineStr">
+        <is>
+          <t>Partición por proyecto (proyectos de prueba no vistos) y, aparte, validación cruzada de 10 pliegues por oración</t>
+        </is>
+      </c>
+      <c r="X122" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y122" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, F1 macro y ponderado, F1 por clase</t>
+        </is>
+      </c>
+      <c r="Z122" s="4" t="inlineStr">
+        <is>
+          <t>0.80 por proyecto frente a 0.97 por oración</t>
+        </is>
+      </c>
+      <c r="AA122" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud 0.86 por proyecto</t>
+        </is>
+      </c>
+      <c r="AB122" s="4" t="inlineStr">
+        <is>
+          <t>Por clase; el contexto del FR ayuda en seguridad y usabilidad, no en disponibilidad</t>
+        </is>
+      </c>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Codificadores generales</t>
+        </is>
+      </c>
+      <c r="AD122" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE122" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF122" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG122" s="4" t="inlineStr">
+        <is>
+          <t>PR1, PR5</t>
+        </is>
+      </c>
+      <c r="AH122" s="4" t="inlineStr">
+        <is>
+          <t>Evidencia directa del efecto del protocolo: el mismo modelo pasa de 0.97 a 0.80 de F1 macro al evaluar en proyectos no vistos. Materiales disponibles solo a pedido.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
@@ -11634,31 +13150,127 @@
           <t>PROMISE; PROMISE_exp; SecReq</t>
         </is>
       </c>
-      <c r="J127" s="4" t="n"/>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K127" s="4" t="n"/>
-      <c r="L127" s="4" t="n"/>
-      <c r="M127" s="4" t="n"/>
-      <c r="N127" s="4" t="n"/>
-      <c r="O127" s="4" t="n"/>
-      <c r="P127" s="4" t="n"/>
-      <c r="Q127" s="4" t="n"/>
-      <c r="R127" s="4" t="n"/>
-      <c r="S127" s="4" t="n"/>
-      <c r="T127" s="4" t="n"/>
-      <c r="U127" s="4" t="n"/>
-      <c r="V127" s="4" t="n"/>
-      <c r="W127" s="4" t="n"/>
-      <c r="X127" s="4" t="n"/>
-      <c r="Y127" s="4" t="n"/>
-      <c r="Z127" s="4" t="n"/>
-      <c r="AA127" s="4" t="n"/>
-      <c r="AB127" s="4" t="n"/>
-      <c r="AC127" s="4" t="n"/>
-      <c r="AD127" s="4" t="n"/>
-      <c r="AE127" s="4" t="n"/>
-      <c r="AF127" s="4" t="n"/>
-      <c r="AG127" s="4" t="n"/>
-      <c r="AH127" s="4" t="n"/>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE (622 tras depurar), PROMISE_exp, Promise+ y SecReq</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>622 y otros</t>
+        </is>
+      </c>
+      <c r="P127" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR; 11 NFR; seguridad</t>
+        </is>
+      </c>
+      <c r="R127" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S127" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (partición estratificada)</t>
+        </is>
+      </c>
+      <c r="T127" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U127" s="4" t="inlineStr">
+        <is>
+          <t>EviReqRAG: recuperación BM25, densa e híbrida con re-ranking; DeepSeek-v4-pro y Claude-Opus-4-8</t>
+        </is>
+      </c>
+      <c r="V127" s="4" t="inlineStr">
+        <is>
+          <t>Clasificador few-shot</t>
+        </is>
+      </c>
+      <c r="W127" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada; los ejemplos recuperados provienen del conjunto de referencia</t>
+        </is>
+      </c>
+      <c r="X127" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y127" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, F1, F1 macro y exactitud balanceada</t>
+        </is>
+      </c>
+      <c r="Z127" s="4" t="inlineStr">
+        <is>
+          <t>NFR multiclase 0.89 (exactitud balanceada 0.92)</t>
+        </is>
+      </c>
+      <c r="AA127" s="4" t="inlineStr">
+        <is>
+          <t>FR/NFR F1 0.94; seguridad F1 0.94</t>
+        </is>
+      </c>
+      <c r="AB127" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud balanceada</t>
+        </is>
+      </c>
+      <c r="AC127" s="4" t="inlineStr">
+        <is>
+          <t>Clasificadores supervisados y transformers de la literatura</t>
+        </is>
+      </c>
+      <c r="AD127" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE127" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF127" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG127" s="4" t="inlineStr">
+        <is>
+          <t>PR3</t>
+        </is>
+      </c>
+      <c r="AH127" s="4" t="inlineStr">
+        <is>
+          <t>Elimina duplicados idénticos y conflictivos (PROMISE queda en 622). Usa un LLM con ejemplos recuperados como evidencia: recuperación aumentada, no aumentación de datos.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -12362,31 +13974,127 @@
           <t>PROMISE_exp</t>
         </is>
       </c>
-      <c r="J134" s="4" t="n"/>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K134" s="4" t="n"/>
-      <c r="L134" s="4" t="n"/>
-      <c r="M134" s="4" t="n"/>
-      <c r="N134" s="4" t="n"/>
-      <c r="O134" s="4" t="n"/>
-      <c r="P134" s="4" t="n"/>
-      <c r="Q134" s="4" t="n"/>
-      <c r="R134" s="4" t="n"/>
-      <c r="S134" s="4" t="n"/>
-      <c r="T134" s="4" t="n"/>
-      <c r="U134" s="4" t="n"/>
-      <c r="V134" s="4" t="n"/>
-      <c r="W134" s="4" t="n"/>
-      <c r="X134" s="4" t="n"/>
-      <c r="Y134" s="4" t="n"/>
-      <c r="Z134" s="4" t="n"/>
-      <c r="AA134" s="4" t="n"/>
-      <c r="AB134" s="4" t="n"/>
-      <c r="AC134" s="4" t="n"/>
-      <c r="AD134" s="4" t="n"/>
-      <c r="AE134" s="4" t="n"/>
-      <c r="AF134" s="4" t="n"/>
-      <c r="AG134" s="4" t="n"/>
-      <c r="AH134" s="4" t="n"/>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>PROMISE_exp traducido al español y PROMISE_exp_balanced; requerimientos originales en español para validación cruzada entre conjuntos</t>
+        </is>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Español</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="P134" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R134" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S134" s="4" t="inlineStr">
+        <is>
+          <t>Sobremuestreo con NFR sintéticos generados con ChatGPT y submuestreo</t>
+        </is>
+      </c>
+      <c r="T134" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="U134" s="4" t="inlineStr">
+        <is>
+          <t>Seis algoritmos (RL, NB, SVM y otros; también DL) con ajuste de hiperparámetros</t>
+        </is>
+      </c>
+      <c r="V134" s="4" t="inlineStr">
+        <is>
+          <t>Generador de datos</t>
+        </is>
+      </c>
+      <c r="W134" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada 80/20 con validación cruzada estratificada en el entrenamiento; prueba en datos no vistos de otro conjunto</t>
+        </is>
+      </c>
+      <c r="X134" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y134" s="4" t="inlineStr">
+        <is>
+          <t>Precisión, exhaustividad y F1 macro y ponderados</t>
+        </is>
+      </c>
+      <c r="Z134" s="4" t="inlineStr">
+        <is>
+          <t>En tablas para ambos conjuntos</t>
+        </is>
+      </c>
+      <c r="AA134" s="4" t="inlineStr">
+        <is>
+          <t>RL 0.82 y NB 0.81 en el conjunto traducido; el balanceo baja el promedio</t>
+        </is>
+      </c>
+      <c r="AB134" s="4" t="inlineStr">
+        <is>
+          <t>El balanceo mejora PO y FT</t>
+        </is>
+      </c>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto traducido sin balancear</t>
+        </is>
+      </c>
+      <c r="AD134" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE134" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF134" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG134" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH134" s="4" t="inlineStr">
+        <is>
+          <t>Único estudio en español con balanceo. Cochran Q y Wilcoxon. Código y datos en Zenodo. El balanceo con LLM mejora clases raras pero baja el desempeño global, coherente con Pham et al.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -12426,8 +14134,16 @@
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr"/>
-      <c r="J135" s="4" t="n"/>
-      <c r="K135" s="4" t="n"/>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>CE2</t>
+        </is>
+      </c>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
@@ -12450,7 +14166,11 @@
       <c r="AE135" s="4" t="n"/>
       <c r="AF135" s="4" t="n"/>
       <c r="AG135" s="4" t="n"/>
-      <c r="AH135" s="4" t="n"/>
+      <c r="AH135" s="4" t="inlineStr">
+        <is>
+          <t>Clasifica reseñas de banca móvil en categorías de Kano (obligatorio, desempeño, atractivo) para priorizar; no son tipos de requerimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -12618,31 +14338,123 @@
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="4" t="n"/>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K138" s="4" t="n"/>
-      <c r="L138" s="4" t="n"/>
-      <c r="M138" s="4" t="n"/>
-      <c r="N138" s="4" t="n"/>
-      <c r="O138" s="4" t="n"/>
-      <c r="P138" s="4" t="n"/>
-      <c r="Q138" s="4" t="n"/>
-      <c r="R138" s="4" t="n"/>
-      <c r="S138" s="4" t="n"/>
-      <c r="T138" s="4" t="n"/>
-      <c r="U138" s="4" t="n"/>
-      <c r="V138" s="4" t="n"/>
-      <c r="W138" s="4" t="n"/>
-      <c r="X138" s="4" t="n"/>
-      <c r="Y138" s="4" t="n"/>
-      <c r="Z138" s="4" t="n"/>
-      <c r="AA138" s="4" t="n"/>
-      <c r="AB138" s="4" t="n"/>
-      <c r="AC138" s="4" t="n"/>
-      <c r="AD138" s="4" t="n"/>
-      <c r="AE138" s="4" t="n"/>
-      <c r="AF138" s="4" t="n"/>
-      <c r="AG138" s="4" t="n"/>
-      <c r="AH138" s="4" t="n"/>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>Conjuntos sintéticos generados con LLM alineados con Volere (≈1000 por categoría), sembrados con PROMISE aumentado</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>≈9000 sintéticos</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="inlineStr">
+        <is>
+          <t>Multiclase NFR</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>9 categorías Volere</t>
+        </is>
+      </c>
+      <c r="R138" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S138" s="4" t="inlineStr">
+        <is>
+          <t>Generación sintética balanceada con LLM (O3DG) y poda de muestras ambiguas</t>
+        </is>
+      </c>
+      <c r="T138" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U138" s="4" t="inlineStr">
+        <is>
+          <t>Modelos ML y DL entrenados con los conjuntos sintéticos</t>
+        </is>
+      </c>
+      <c r="V138" s="4" t="inlineStr">
+        <is>
+          <t>Generador de datos</t>
+        </is>
+      </c>
+      <c r="W138" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada k-fold con parada temprana sobre los conjuntos sintéticos; revisión por cuatro expertos</t>
+        </is>
+      </c>
+      <c r="X138" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Y138" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud, F1, precisión y exhaustividad</t>
+        </is>
+      </c>
+      <c r="Z138" s="4" t="inlineStr"/>
+      <c r="AA138" s="4" t="inlineStr">
+        <is>
+          <t>Reportados por modelo en el texto</t>
+        </is>
+      </c>
+      <c r="AB138" s="4" t="inlineStr">
+        <is>
+          <t>No aplica (conjunto balanceado)</t>
+        </is>
+      </c>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Conjuntos públicos como PROMISE</t>
+        </is>
+      </c>
+      <c r="AD138" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE138" s="4" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="AF138" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG138" s="4" t="inlineStr">
+        <is>
+          <t>PR2, PR4</t>
+        </is>
+      </c>
+      <c r="AH138" s="4" t="inlineStr">
+        <is>
+          <t>Los NFR generados tienden a ser genéricos y parecidos entre sí. Las semillas de PROMISE aumentado tienen etiquetas erróneas. Valida con expertos y con clasificadores, no probando en datos reales.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -13102,31 +14914,123 @@
           <t>PROMISE</t>
         </is>
       </c>
-      <c r="J144" s="4" t="n"/>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K144" s="4" t="n"/>
-      <c r="L144" s="4" t="n"/>
-      <c r="M144" s="4" t="n"/>
-      <c r="N144" s="4" t="n"/>
-      <c r="O144" s="4" t="n"/>
-      <c r="P144" s="4" t="n"/>
-      <c r="Q144" s="4" t="n"/>
-      <c r="R144" s="4" t="n"/>
-      <c r="S144" s="4" t="n"/>
-      <c r="T144" s="4" t="n"/>
-      <c r="U144" s="4" t="n"/>
-      <c r="V144" s="4" t="n"/>
-      <c r="W144" s="4" t="n"/>
-      <c r="X144" s="4" t="n"/>
-      <c r="Y144" s="4" t="n"/>
-      <c r="Z144" s="4" t="n"/>
-      <c r="AA144" s="4" t="n"/>
-      <c r="AB144" s="4" t="n"/>
-      <c r="AC144" s="4" t="n"/>
-      <c r="AD144" s="4" t="n"/>
-      <c r="AE144" s="4" t="n"/>
-      <c r="AF144" s="4" t="n"/>
-      <c r="AG144" s="4" t="n"/>
-      <c r="AH144" s="4" t="n"/>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>SecReq combinado con PROMISE NFR</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>SecReq + 625</t>
+        </is>
+      </c>
+      <c r="P144" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>2 (seguridad / no seguridad)</t>
+        </is>
+      </c>
+      <c r="R144" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S144" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna (métricas ponderadas)</t>
+        </is>
+      </c>
+      <c r="T144" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U144" s="4" t="inlineStr">
+        <is>
+          <t>SeqFAL: aprendizaje activo federado con embeddings MiniLM y clasificadores lineales</t>
+        </is>
+      </c>
+      <c r="V144" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W144" s="4" t="inlineStr">
+        <is>
+          <t>Partición 70/30 fija; prueba nunca usada en entrenamiento; varias semillas</t>
+        </is>
+      </c>
+      <c r="X144" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y144" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud y precisión, exhaustividad y F1 ponderados</t>
+        </is>
+      </c>
+      <c r="Z144" s="4" t="inlineStr"/>
+      <c r="AA144" s="4" t="inlineStr">
+        <is>
+          <t>Comparable al aprendizaje activo centralizado con menos etiquetas</t>
+        </is>
+      </c>
+      <c r="AB144" s="4" t="inlineStr">
+        <is>
+          <t>No se reporta</t>
+        </is>
+      </c>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Centralizado, FL sin AL y AL sin FL</t>
+        </is>
+      </c>
+      <c r="AD144" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE144" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF144" s="4" t="inlineStr">
+        <is>
+          <t>Sección de amenazas a la validez</t>
+        </is>
+      </c>
+      <c r="AG144" s="4" t="inlineStr">
+        <is>
+          <t>PR4</t>
+        </is>
+      </c>
+      <c r="AH144" s="4" t="inlineStr">
+        <is>
+          <t>Friedman, Nemenyi y W de Kendall. Código en GitHub (waadalhoshan/SeqFAL). Vía para etiquetar con menos esfuerzo sin compartir datos.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -13162,31 +15066,123 @@
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr"/>
-      <c r="J145" s="4" t="n"/>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="K145" s="4" t="n"/>
-      <c r="L145" s="4" t="n"/>
-      <c r="M145" s="4" t="n"/>
-      <c r="N145" s="4" t="n"/>
-      <c r="O145" s="4" t="n"/>
-      <c r="P145" s="4" t="n"/>
-      <c r="Q145" s="4" t="n"/>
-      <c r="R145" s="4" t="n"/>
-      <c r="S145" s="4" t="n"/>
-      <c r="T145" s="4" t="n"/>
-      <c r="U145" s="4" t="n"/>
-      <c r="V145" s="4" t="n"/>
-      <c r="W145" s="4" t="n"/>
-      <c r="X145" s="4" t="n"/>
-      <c r="Y145" s="4" t="n"/>
-      <c r="Z145" s="4" t="n"/>
-      <c r="AA145" s="4" t="n"/>
-      <c r="AB145" s="4" t="n"/>
-      <c r="AC145" s="4" t="n"/>
-      <c r="AD145" s="4" t="n"/>
-      <c r="AE145" s="4" t="n"/>
-      <c r="AF145" s="4" t="n"/>
-      <c r="AG145" s="4" t="n"/>
-      <c r="AH145" s="4" t="n"/>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas/feedback</t>
+        </is>
+      </c>
+      <c r="M145" s="4" t="inlineStr">
+        <is>
+          <t>Reseñas de apps (de más de un millón) etiquetadas con filtrado por palabras clave, expertos y aprendizaje activo</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>No se precisa en el texto revisado</t>
+        </is>
+      </c>
+      <c r="P145" s="4" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="Q145" s="4" t="inlineStr">
+        <is>
+          <t>2 (relacionada o no con seguridad)</t>
+        </is>
+      </c>
+      <c r="R145" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S145" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="T145" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="U145" s="4" t="inlineStr">
+        <is>
+          <t>SBERT y Paraphrase ajustados; ML clásico como línea base; LLM solo para explicar</t>
+        </is>
+      </c>
+      <c r="V145" s="4" t="inlineStr">
+        <is>
+          <t>No usa LLM</t>
+        </is>
+      </c>
+      <c r="W145" s="4" t="inlineStr">
+        <is>
+          <t>Validación cruzada de 10 pliegues y conjunto de prueba separado con reseñas no vistas</t>
+        </is>
+      </c>
+      <c r="X145" s="4" t="inlineStr">
+        <is>
+          <t>No se indica</t>
+        </is>
+      </c>
+      <c r="Y145" s="4" t="inlineStr">
+        <is>
+          <t>Exactitud y F1</t>
+        </is>
+      </c>
+      <c r="Z145" s="4" t="inlineStr"/>
+      <c r="AA145" s="4" t="inlineStr">
+        <is>
+          <t>SBERT: 0.887 en validación cruzada frente a 0.710 en la prueba separada; Paraphrase 0.904 y 0.911</t>
+        </is>
+      </c>
+      <c r="AB145" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="AC145" s="4" t="inlineStr">
+        <is>
+          <t>KNN, SVM, LightGBM y RF</t>
+        </is>
+      </c>
+      <c r="AD145" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE145" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF145" s="4" t="inlineStr">
+        <is>
+          <t>Sección de limitaciones</t>
+        </is>
+      </c>
+      <c r="AG145" s="4" t="inlineStr">
+        <is>
+          <t>PR4, PR5</t>
+        </is>
+      </c>
+      <c r="AH145" s="4" t="inlineStr">
+        <is>
+          <t>McNemar y prueba t pareada. La caída de SBERT de 0.89 a 0.71 entre la validación cruzada y la prueba separada ilustra la sobreestimación por protocolo.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
@@ -14507,20 +16503,60 @@
           <t>Software Requirements Classification using Deep-learning Approach with Various Hidden Layers</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L28" s="6">
         <f>IF(COUNTA(D28:K28)=0,"",COUNTIF(D28:K28,"Sí")+0.5*COUNTIF(D28:K28,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="6" t="n"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: SMOTE antes de la validación cruzada.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -14561,20 +16597,60 @@
           <t>A Novel Hybrid Deep Learning Model for Detecting and Classifying Non-Functional Requirements of Mobile Apps Issues</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L30" s="6">
         <f>IF(COUNTA(D30:K30)=0,"",COUNTIF(D30:K30,"Sí")+0.5*COUNTIF(D30:K30,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: partición no descrita.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -14709,20 +16785,60 @@
           <t>Developing an Advanced Software Requirements Classification Model Using BERT: An Empirical Evaluation Study on Newly Generated Turkish Data</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L34" s="6">
         <f>IF(COUNTA(D34:K34)=0,"",COUNTIF(D34:K34,"Sí")+0.5*COUNTIF(D34:K34,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M34" s="6" t="n"/>
-      <c r="N34" s="6" t="n"/>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>QA4 = 0: F-score global binario.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -14857,20 +16973,60 @@
           <t>Non Functional Requirements Identification and Classification Using Transfer Learning Model</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L38" s="6">
         <f>IF(COUNTA(D38:K38)=0,"",COUNTIF(D38:K38,"Sí")+0.5*COUNTIF(D38:K38,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M38" s="6" t="n"/>
-      <c r="N38" s="6" t="n"/>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: MCC y matriz de confusión, sin F1 macro.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -15032,20 +17188,60 @@
           <t>Classifying software security requirements into confidentiality, integrity, and availability using machine learning approaches</t>
         </is>
       </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L43" s="6">
         <f>IF(COUNTA(D43:K43)=0,"",COUNTIF(D43:K43,"Sí")+0.5*COUNTIF(D43:K43,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M43" s="6" t="n"/>
-      <c r="N43" s="6" t="n"/>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 sin promedio especificado.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -15113,20 +17309,60 @@
           <t>EnsCL-CatBoost: A Strategic Framework for Software Requirements Classification</t>
         </is>
       </c>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L46" s="6">
         <f>IF(COUNTA(D46:K46)=0,"",COUNTIF(D46:K46,"Sí")+0.5*COUNTIF(D46:K46,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="6" t="n"/>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: SMOTE-Tomek antes de la partición.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -15799,20 +18035,60 @@
           <t>Automated Classification and Identification of Non-Functional Requirements in Agile-Based Requirements Using Pre-Trained Language Models</t>
         </is>
       </c>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-      <c r="J64" s="7" t="n"/>
-      <c r="K64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L64" s="6">
         <f>IF(COUNTA(D64:K64)=0,"",COUNTIF(D64:K64,"Sí")+0.5*COUNTIF(D64:K64,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M64" s="6" t="n"/>
-      <c r="N64" s="6" t="n"/>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 sin promedio macro explícito.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -15934,20 +18210,60 @@
           <t>BERT Fine-Tuning for Software Requirement Classification: Impact of Model Components and Dataset Size</t>
         </is>
       </c>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-      <c r="J69" s="7" t="n"/>
-      <c r="K69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L69" s="6">
         <f>IF(COUNTA(D69:K69)=0,"",COUNTIF(D69:K69,"Sí")+0.5*COUNTIF(D69:K69,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M69" s="6" t="n"/>
-      <c r="N69" s="6" t="n"/>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: F1 por clase en tarea binaria.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -16364,20 +18680,60 @@
           <t>Enhancing Software Sustainability: Leveraging Large Language Models to Evaluate Security Requirements Fulfillment in Requirements Engineering</t>
         </is>
       </c>
-      <c r="D79" s="7" t="n"/>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="n"/>
-      <c r="G79" s="7" t="n"/>
-      <c r="H79" s="7" t="n"/>
-      <c r="I79" s="7" t="n"/>
-      <c r="J79" s="7" t="n"/>
-      <c r="K79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L79" s="6">
         <f>IF(COUNTA(D79:K79)=0,"",COUNTIF(D79:K79,"Sí")+0.5*COUNTIF(D79:K79,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M79" s="6" t="n"/>
-      <c r="N79" s="6" t="n"/>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>QA3 = 0: sin conjunto de prueba separado descrito.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -16445,20 +18801,60 @@
           <t>Explainable Security Requirements Classification Through Transformer Models</t>
         </is>
       </c>
-      <c r="D82" s="7" t="n"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="n"/>
-      <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="n"/>
-      <c r="J82" s="7" t="n"/>
-      <c r="K82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L82" s="6">
         <f>IF(COUNTA(D82:K82)=0,"",COUNTIF(D82:K82,"Sí")+0.5*COUNTIF(D82:K82,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M82" s="6" t="n"/>
-      <c r="N82" s="6" t="n"/>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>QA3: aumenta solo el entrenamiento. QA4 parcial: métricas binarias.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -16754,20 +19150,60 @@
           <t>How Reliable Are GPT-4o and LLAMA3.3-70B in Classifying Natural Language Requirements?: The Impact of the Temperature Setting</t>
         </is>
       </c>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-      <c r="J89" s="7" t="n"/>
-      <c r="K89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L89" s="6">
         <f>IF(COUNTA(D89:K89)=0,"",COUNTIF(D89:K89,"Sí")+0.5*COUNTIF(D89:K89,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M89" s="6" t="n"/>
-      <c r="N89" s="6" t="n"/>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>QA6: tres ejecuciones y pruebas de acuerdo.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -17238,20 +19674,60 @@
           <t>On the Effectiveness of Zero-Shot and Few-Shot Pretrained Language Models for Software Requirement Classification</t>
         </is>
       </c>
-      <c r="D101" s="7" t="n"/>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="7" t="n"/>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
-      <c r="J101" s="7" t="n"/>
-      <c r="K101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L101" s="6">
         <f>IF(COUNTA(D101:K101)=0,"",COUNTIF(D101:K101,"Sí")+0.5*COUNTIF(D101:K101,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M101" s="6" t="n"/>
-      <c r="N101" s="6" t="n"/>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>Cumple los ocho criterios.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -17642,20 +20118,60 @@
           <t>A knowledge-driven semantic framework for non-functional requirement engineering in intelligent healthcare systems</t>
         </is>
       </c>
-      <c r="D113" s="7" t="n"/>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="7" t="n"/>
-      <c r="G113" s="7" t="n"/>
-      <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
-      <c r="J113" s="7" t="n"/>
-      <c r="K113" s="7" t="n"/>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I113" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L113" s="6">
         <f>IF(COUNTA(D113:K113)=0,"",COUNTIF(D113:K113,"Sí")+0.5*COUNTIF(D113:K113,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M113" s="6" t="n"/>
-      <c r="N113" s="6" t="n"/>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>QA2 parcial: no da la distribución de las cinco clases.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -17669,20 +20185,60 @@
           <t>Adaptive Data Augmentation Techniques for Software Requirements Classification Using Deep Learning</t>
         </is>
       </c>
-      <c r="D114" s="7" t="n"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="7" t="n"/>
-      <c r="G114" s="7" t="n"/>
-      <c r="H114" s="7" t="n"/>
-      <c r="I114" s="7" t="n"/>
-      <c r="J114" s="7" t="n"/>
-      <c r="K114" s="7" t="n"/>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I114" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
       <c r="L114" s="6">
         <f>IF(COUNTA(D114:K114)=0,"",COUNTIF(D114:K114,"Sí")+0.5*COUNTIF(D114:K114,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M114" s="6" t="n"/>
-      <c r="N114" s="6" t="n"/>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>QA3: aumenta solo el entrenamiento. QA4: F1 macro y por clase.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -17723,20 +20279,60 @@
           <t>An Intelligent Model to Predict Functional and Non-Functional Requirements From Software Requirements Specification</t>
         </is>
       </c>
-      <c r="D116" s="7" t="n"/>
-      <c r="E116" s="7" t="n"/>
-      <c r="F116" s="7" t="n"/>
-      <c r="G116" s="7" t="n"/>
-      <c r="H116" s="7" t="n"/>
-      <c r="I116" s="7" t="n"/>
-      <c r="J116" s="7" t="n"/>
-      <c r="K116" s="7" t="n"/>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L116" s="6">
         <f>IF(COUNTA(D116:K116)=0,"",COUNTIF(D116:K116,"Sí")+0.5*COUNTIF(D116:K116,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M116" s="6" t="n"/>
-      <c r="N116" s="6" t="n"/>
+      <c r="M116" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N116" s="6" t="inlineStr">
+        <is>
+          <t>Cumple los ocho criterios.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -17925,20 +20521,60 @@
           <t>Context-Aware Non-Functional Requirement Classification Using Functional Requirement Guidance and Domain-Specialized Representations</t>
         </is>
       </c>
-      <c r="D122" s="7" t="n"/>
-      <c r="E122" s="7" t="n"/>
-      <c r="F122" s="7" t="n"/>
-      <c r="G122" s="7" t="n"/>
-      <c r="H122" s="7" t="n"/>
-      <c r="I122" s="7" t="n"/>
-      <c r="J122" s="7" t="n"/>
-      <c r="K122" s="7" t="n"/>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L122" s="6">
         <f>IF(COUNTA(D122:K122)=0,"",COUNTIF(D122:K122,"Sí")+0.5*COUNTIF(D122:K122,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M122" s="6" t="n"/>
-      <c r="N122" s="6" t="n"/>
+      <c r="M122" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N122" s="6" t="inlineStr">
+        <is>
+          <t>QA3: partición por proyecto. QA7 = 0: materiales solo a pedido.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
@@ -18140,20 +20776,60 @@
           <t>EviReqRAG: An Evidence-Based Retrieval-Augmented Generation Framework for Software Requirements and Security Classification</t>
         </is>
       </c>
-      <c r="D127" s="7" t="n"/>
-      <c r="E127" s="7" t="n"/>
-      <c r="F127" s="7" t="n"/>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="7" t="n"/>
-      <c r="I127" s="7" t="n"/>
-      <c r="J127" s="7" t="n"/>
-      <c r="K127" s="7" t="n"/>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L127" s="6">
         <f>IF(COUNTA(D127:K127)=0,"",COUNTIF(D127:K127,"Sí")+0.5*COUNTIF(D127:K127,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M127" s="6" t="n"/>
-      <c r="N127" s="6" t="n"/>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N127" s="6" t="inlineStr">
+        <is>
+          <t>QA3: depura duplicados antes de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n">
@@ -18449,20 +21125,60 @@
           <t>Improving the Multi-Class Classification of Non-Functional Requirements in Spanish: A Study of Dataset Balancing and Performance</t>
         </is>
       </c>
-      <c r="D134" s="7" t="n"/>
-      <c r="E134" s="7" t="n"/>
-      <c r="F134" s="7" t="n"/>
-      <c r="G134" s="7" t="n"/>
-      <c r="H134" s="7" t="n"/>
-      <c r="I134" s="7" t="n"/>
-      <c r="J134" s="7" t="n"/>
-      <c r="K134" s="7" t="n"/>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L134" s="6">
         <f>IF(COUNTA(D134:K134)=0,"",COUNTIF(D134:K134,"Sí")+0.5*COUNTIF(D134:K134,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M134" s="6" t="n"/>
-      <c r="N134" s="6" t="n"/>
+      <c r="M134" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N134" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: no queda claro si el conjunto balanceado se construyó solo con el entrenamiento.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
@@ -18557,20 +21273,60 @@
           <t>On-demand generation of high-quality software engineering datasets using large language models and ontologies</t>
         </is>
       </c>
-      <c r="D138" s="7" t="n"/>
-      <c r="E138" s="7" t="n"/>
-      <c r="F138" s="7" t="n"/>
-      <c r="G138" s="7" t="n"/>
-      <c r="H138" s="7" t="n"/>
-      <c r="I138" s="7" t="n"/>
-      <c r="J138" s="7" t="n"/>
-      <c r="K138" s="7" t="n"/>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L138" s="6">
         <f>IF(COUNTA(D138:K138)=0,"",COUNTIF(D138:K138,"Sí")+0.5*COUNTIF(D138:K138,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M138" s="6" t="n"/>
-      <c r="N138" s="6" t="n"/>
+      <c r="M138" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N138" s="6" t="inlineStr">
+        <is>
+          <t>QA3 parcial: evaluación sobre datos sintéticos.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
@@ -18759,20 +21515,60 @@
           <t>SeqFAL: A Federated Active Learning Framework for Private and Efficient Labeling of Security Requirements</t>
         </is>
       </c>
-      <c r="D144" s="7" t="n"/>
-      <c r="E144" s="7" t="n"/>
-      <c r="F144" s="7" t="n"/>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="7" t="n"/>
-      <c r="I144" s="7" t="n"/>
-      <c r="J144" s="7" t="n"/>
-      <c r="K144" s="7" t="n"/>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L144" s="6">
         <f>IF(COUNTA(D144:K144)=0,"",COUNTIF(D144:K144,"Sí")+0.5*COUNTIF(D144:K144,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M144" s="6" t="n"/>
-      <c r="N144" s="6" t="n"/>
+      <c r="M144" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N144" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: métricas ponderadas.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
@@ -18786,20 +21582,60 @@
           <t>Transformer-Based Classification of Security-Related Mobile App Reviews Using Active Learning</t>
         </is>
       </c>
-      <c r="D145" s="7" t="n"/>
-      <c r="E145" s="7" t="n"/>
-      <c r="F145" s="7" t="n"/>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="7" t="n"/>
-      <c r="I145" s="7" t="n"/>
-      <c r="J145" s="7" t="n"/>
-      <c r="K145" s="7" t="n"/>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="L145" s="6">
         <f>IF(COUNTA(D145:K145)=0,"",COUNTIF(D145:K145,"Sí")+0.5*COUNTIF(D145:K145,"Parcial"))</f>
         <v/>
       </c>
-      <c r="M145" s="6" t="n"/>
-      <c r="N145" s="6" t="n"/>
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>Revisor 1 (asistido por IA)</t>
+        </is>
+      </c>
+      <c r="N145" s="6" t="inlineStr">
+        <is>
+          <t>QA4 parcial: métricas binarias.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n">
